--- a/psychopy_exp_files/sequences/retrieval_block1_fixed-middle-10_48.xlsx
+++ b/psychopy_exp_files/sequences/retrieval_block1_fixed-middle-10_48.xlsx
@@ -552,12 +552,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -585,7 +585,7 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O2" t="n">
         <v>1.2</v>
@@ -630,12 +630,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -649,7 +649,7 @@
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O3" t="n">
         <v>2</v>
@@ -690,12 +690,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_49.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>stimuli/house/house_50.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -723,7 +723,7 @@
         <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O4" t="n">
         <v>1.2</v>
@@ -768,12 +768,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_49.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>stimuli/house/house_50.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -787,7 +787,7 @@
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O5" t="n">
         <v>2</v>
@@ -828,12 +828,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -861,7 +861,7 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O6" t="n">
         <v>1.2</v>
@@ -906,12 +906,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -925,7 +925,7 @@
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O7" t="n">
         <v>2</v>
@@ -966,12 +966,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_28.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_41.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -999,7 +999,7 @@
         <v>1</v>
       </c>
       <c r="N8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O8" t="n">
         <v>1.2</v>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_28.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_41.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O9" t="n">
         <v>2</v>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_02.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -1137,7 +1137,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O10" t="n">
         <v>1.2</v>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_02.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O11" t="n">
         <v>2</v>
@@ -1242,12 +1242,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_14.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_28.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -1275,7 +1275,7 @@
         <v>1</v>
       </c>
       <c r="N12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O12" t="n">
         <v>1.2</v>
@@ -1320,12 +1320,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_14.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_28.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O13" t="n">
         <v>2</v>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_49.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -1413,7 +1413,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O14" t="n">
         <v>1.2</v>
@@ -1458,12 +1458,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_49.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O15" t="n">
         <v>2</v>
@@ -1518,12 +1518,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_41.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -1551,7 +1551,7 @@
         <v>1</v>
       </c>
       <c r="N16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O16" t="n">
         <v>1.2</v>
@@ -1596,12 +1596,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_41.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O17" t="n">
         <v>2</v>
@@ -1656,12 +1656,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_02.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_49.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -1689,7 +1689,7 @@
         <v>1</v>
       </c>
       <c r="N18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O18" t="n">
         <v>1.2</v>
@@ -1734,12 +1734,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_02.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_49.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O19" t="n">
         <v>2</v>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_14.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -1827,7 +1827,7 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O20" t="n">
         <v>1.2</v>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_14.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O21" t="n">
         <v>2</v>
@@ -1932,12 +1932,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>stimuli/house/house_50.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
@@ -1965,7 +1965,7 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O22" t="n">
         <v>1.2</v>
@@ -2010,12 +2010,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>stimuli/house/house_50.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O23" t="n">
         <v>2</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_41.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -2103,7 +2103,7 @@
         <v>1</v>
       </c>
       <c r="N24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O24" t="n">
         <v>1.2</v>
@@ -2148,12 +2148,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_41.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -2167,7 +2167,7 @@
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O25" t="n">
         <v>2</v>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_14.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
@@ -2241,7 +2241,7 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O26" t="n">
         <v>1.2</v>
@@ -2286,12 +2286,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_14.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
@@ -2305,7 +2305,7 @@
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O27" t="n">
         <v>2</v>
@@ -2346,12 +2346,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_41.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
@@ -2379,7 +2379,7 @@
         <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O28" t="n">
         <v>1.2</v>
@@ -2424,12 +2424,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_41.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O29" t="n">
         <v>2</v>
@@ -2484,12 +2484,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_49.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
@@ -2517,7 +2517,7 @@
         <v>1</v>
       </c>
       <c r="N30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O30" t="n">
         <v>1.2</v>
@@ -2562,12 +2562,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_49.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O31" t="n">
         <v>2</v>
@@ -2622,12 +2622,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_28.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_02.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O32" t="n">
         <v>1.2</v>
@@ -2700,12 +2700,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_28.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_02.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O33" t="n">
         <v>2</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
@@ -2793,7 +2793,7 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O34" t="n">
         <v>1.2</v>
@@ -2838,12 +2838,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O35" t="n">
         <v>2</v>
@@ -2898,12 +2898,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_02.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
@@ -2931,7 +2931,7 @@
         <v>1</v>
       </c>
       <c r="N36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O36" t="n">
         <v>1.2</v>
@@ -2976,12 +2976,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_02.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
@@ -2995,7 +2995,7 @@
       </c>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O37" t="n">
         <v>2</v>
@@ -3036,12 +3036,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_14.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -3069,7 +3069,7 @@
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O38" t="n">
         <v>1.2</v>
@@ -3114,12 +3114,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_14.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
@@ -3133,7 +3133,7 @@
       </c>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O39" t="n">
         <v>2</v>
@@ -3174,12 +3174,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_28.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>stimuli/house/house_50.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
@@ -3207,7 +3207,7 @@
         <v>1</v>
       </c>
       <c r="N40" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O40" t="n">
         <v>1.2</v>
@@ -3252,12 +3252,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_28.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>stimuli/house/house_50.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O41" t="n">
         <v>2</v>
@@ -3312,12 +3312,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_49.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_02.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
@@ -3345,7 +3345,7 @@
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O42" t="n">
         <v>1.2</v>
@@ -3390,12 +3390,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_49.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_02.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O43" t="n">
         <v>2</v>
@@ -3450,12 +3450,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>stimuli/house/house_50.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
@@ -3483,7 +3483,7 @@
         <v>1</v>
       </c>
       <c r="N44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O44" t="n">
         <v>1.2</v>
@@ -3528,12 +3528,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>stimuli/house/house_50.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
@@ -3547,7 +3547,7 @@
       </c>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O45" t="n">
         <v>2</v>
@@ -3588,12 +3588,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_28.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_41.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
@@ -3621,7 +3621,7 @@
         <v>1</v>
       </c>
       <c r="N46" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O46" t="n">
         <v>1.2</v>
@@ -3666,12 +3666,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_28.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_41.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O47" t="n">
         <v>2</v>
@@ -3726,12 +3726,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
@@ -3759,7 +3759,7 @@
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O48" t="n">
         <v>1.2</v>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
@@ -3823,7 +3823,7 @@
       </c>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O49" t="n">
         <v>2</v>
@@ -3864,12 +3864,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_02.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
@@ -3897,7 +3897,7 @@
         <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O50" t="n">
         <v>1.2</v>
@@ -3942,12 +3942,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_02.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
@@ -3961,7 +3961,7 @@
       </c>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O51" t="n">
         <v>2</v>
@@ -4002,12 +4002,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_14.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
@@ -4035,7 +4035,7 @@
         <v>1</v>
       </c>
       <c r="N52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O52" t="n">
         <v>1.2</v>
@@ -4080,12 +4080,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_14.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
@@ -4099,7 +4099,7 @@
       </c>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O53" t="n">
         <v>2</v>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_49.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_28.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
@@ -4173,7 +4173,7 @@
         <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O54" t="n">
         <v>1.2</v>
@@ -4218,12 +4218,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_49.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_28.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
@@ -4237,7 +4237,7 @@
       </c>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O55" t="n">
         <v>2</v>
@@ -4278,12 +4278,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
@@ -4311,7 +4311,7 @@
         <v>1</v>
       </c>
       <c r="N56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O56" t="n">
         <v>1.2</v>
@@ -4356,12 +4356,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
@@ -4375,7 +4375,7 @@
       </c>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O57" t="n">
         <v>2</v>
@@ -4416,12 +4416,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_41.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
@@ -4449,7 +4449,7 @@
         <v>1</v>
       </c>
       <c r="N58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O58" t="n">
         <v>1.2</v>
@@ -4494,12 +4494,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_41.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
@@ -4513,7 +4513,7 @@
       </c>
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O59" t="n">
         <v>2</v>
@@ -4554,12 +4554,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_49.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
@@ -4587,7 +4587,7 @@
         <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O60" t="n">
         <v>1.2</v>
@@ -4632,12 +4632,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_49.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O61" t="n">
         <v>2</v>
@@ -4692,12 +4692,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>stimuli/house/house_50.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_28.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
@@ -4725,7 +4725,7 @@
         <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O62" t="n">
         <v>1.2</v>
@@ -4770,12 +4770,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>stimuli/house/house_50.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_28.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
@@ -4789,7 +4789,7 @@
       </c>
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O63" t="n">
         <v>2</v>
@@ -4830,12 +4830,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_14.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
@@ -4863,7 +4863,7 @@
         <v>1</v>
       </c>
       <c r="N64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O64" t="n">
         <v>1.2</v>
@@ -4908,12 +4908,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_14.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
@@ -4927,7 +4927,7 @@
       </c>
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O65" t="n">
         <v>2</v>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
@@ -5001,7 +5001,7 @@
         <v>1</v>
       </c>
       <c r="N66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O66" t="n">
         <v>1.2</v>
@@ -5046,12 +5046,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
@@ -5065,7 +5065,7 @@
       </c>
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O67" t="n">
         <v>2</v>
@@ -5106,12 +5106,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_41.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
@@ -5139,7 +5139,7 @@
         <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O68" t="n">
         <v>1.2</v>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_41.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O69" t="n">
         <v>2</v>
@@ -5244,12 +5244,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_14.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_28.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
@@ -5277,7 +5277,7 @@
         <v>1</v>
       </c>
       <c r="N70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O70" t="n">
         <v>1.2</v>
@@ -5322,12 +5322,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_14.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_28.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
@@ -5341,7 +5341,7 @@
       </c>
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O71" t="n">
         <v>2</v>
@@ -5382,12 +5382,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_49.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
@@ -5415,7 +5415,7 @@
         <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O72" t="n">
         <v>1.2</v>
@@ -5460,12 +5460,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_49.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
@@ -5479,7 +5479,7 @@
       </c>
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O73" t="n">
         <v>2</v>
@@ -5520,12 +5520,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_02.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_28.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
@@ -5553,7 +5553,7 @@
         <v>1</v>
       </c>
       <c r="N74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O74" t="n">
         <v>1.2</v>
@@ -5598,12 +5598,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_02.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_28.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
@@ -5617,7 +5617,7 @@
       </c>
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O75" t="n">
         <v>2</v>
@@ -5658,12 +5658,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_41.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
@@ -5691,7 +5691,7 @@
         <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O76" t="n">
         <v>1.2</v>
@@ -5736,12 +5736,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_41.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
@@ -5755,7 +5755,7 @@
       </c>
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O77" t="n">
         <v>2</v>
@@ -5796,12 +5796,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_49.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
@@ -5829,7 +5829,7 @@
         <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O78" t="n">
         <v>1.2</v>
@@ -5874,12 +5874,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_49.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O79" t="n">
         <v>2</v>
@@ -5934,12 +5934,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_14.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
@@ -5967,7 +5967,7 @@
         <v>1</v>
       </c>
       <c r="N80" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O80" t="n">
         <v>1.2</v>
@@ -6012,12 +6012,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_14.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
@@ -6031,7 +6031,7 @@
       </c>
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O81" t="n">
         <v>2</v>
@@ -6072,12 +6072,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_49.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
@@ -6105,7 +6105,7 @@
         <v>1</v>
       </c>
       <c r="N82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O82" t="n">
         <v>1.2</v>
@@ -6150,12 +6150,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_49.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
@@ -6169,7 +6169,7 @@
       </c>
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O83" t="n">
         <v>2</v>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_41.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
@@ -6243,7 +6243,7 @@
         <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O84" t="n">
         <v>1.2</v>
@@ -6288,12 +6288,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_41.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
@@ -6307,7 +6307,7 @@
       </c>
       <c r="M85" t="inlineStr"/>
       <c r="N85" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O85" t="n">
         <v>2</v>
@@ -6348,12 +6348,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_28.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
@@ -6381,7 +6381,7 @@
         <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O86" t="n">
         <v>1.2</v>
@@ -6426,12 +6426,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_28.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
@@ -6445,7 +6445,7 @@
       </c>
       <c r="M87" t="inlineStr"/>
       <c r="N87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O87" t="n">
         <v>2</v>
@@ -6486,12 +6486,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>stimuli/house/house_50.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
@@ -6519,7 +6519,7 @@
         <v>1</v>
       </c>
       <c r="N88" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O88" t="n">
         <v>1.2</v>
@@ -6564,12 +6564,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>stimuli/house/house_50.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
@@ -6583,7 +6583,7 @@
       </c>
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O89" t="n">
         <v>2</v>
@@ -6624,12 +6624,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_02.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_49.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
@@ -6657,7 +6657,7 @@
         <v>1</v>
       </c>
       <c r="N90" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O90" t="n">
         <v>1.2</v>
@@ -6702,12 +6702,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_02.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_49.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
@@ -6721,7 +6721,7 @@
       </c>
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O91" t="n">
         <v>2</v>
@@ -6762,12 +6762,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_14.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
@@ -6795,7 +6795,7 @@
         <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O92" t="n">
         <v>1.2</v>
@@ -6840,12 +6840,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_14.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
@@ -6859,7 +6859,7 @@
       </c>
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O93" t="n">
         <v>2</v>
@@ -6900,12 +6900,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
@@ -6933,7 +6933,7 @@
         <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O94" t="n">
         <v>1.2</v>
@@ -6978,12 +6978,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
@@ -6997,7 +6997,7 @@
       </c>
       <c r="M95" t="inlineStr"/>
       <c r="N95" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O95" t="n">
         <v>2</v>
@@ -7038,12 +7038,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_41.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
@@ -7071,7 +7071,7 @@
         <v>1</v>
       </c>
       <c r="N96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O96" t="n">
         <v>1.2</v>
@@ -7116,12 +7116,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_41.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
@@ -7135,7 +7135,7 @@
       </c>
       <c r="M97" t="inlineStr"/>
       <c r="N97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O97" t="n">
         <v>2</v>
@@ -7176,12 +7176,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_14.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_28.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
@@ -7209,7 +7209,7 @@
         <v>1</v>
       </c>
       <c r="N98" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O98" t="n">
         <v>1.2</v>
@@ -7254,12 +7254,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_14.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_28.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="H99" t="inlineStr"/>
@@ -7273,7 +7273,7 @@
       </c>
       <c r="M99" t="inlineStr"/>
       <c r="N99" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O99" t="n">
         <v>2</v>
@@ -7314,12 +7314,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_02.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
@@ -7347,7 +7347,7 @@
         <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O100" t="n">
         <v>1.2</v>
@@ -7392,12 +7392,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_02.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
@@ -7411,7 +7411,7 @@
       </c>
       <c r="M101" t="inlineStr"/>
       <c r="N101" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O101" t="n">
         <v>2</v>
@@ -7452,12 +7452,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>stimuli/house/house_50.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_49.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
@@ -7485,7 +7485,7 @@
         <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O102" t="n">
         <v>1.2</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>stimuli/house/house_50.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_49.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="H103" t="inlineStr"/>
@@ -7549,7 +7549,7 @@
       </c>
       <c r="M103" t="inlineStr"/>
       <c r="N103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O103" t="n">
         <v>2</v>
@@ -7590,12 +7590,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="H104" t="inlineStr"/>
@@ -7623,7 +7623,7 @@
         <v>1</v>
       </c>
       <c r="N104" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O104" t="n">
         <v>1.2</v>
@@ -7668,12 +7668,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
@@ -7687,7 +7687,7 @@
       </c>
       <c r="M105" t="inlineStr"/>
       <c r="N105" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O105" t="n">
         <v>2</v>
@@ -7728,12 +7728,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_14.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
@@ -7761,7 +7761,7 @@
         <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O106" t="n">
         <v>1.2</v>
@@ -7806,12 +7806,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_14.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
@@ -7825,7 +7825,7 @@
       </c>
       <c r="M107" t="inlineStr"/>
       <c r="N107" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O107" t="n">
         <v>2</v>
@@ -7866,12 +7866,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_02.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_28.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
@@ -7899,7 +7899,7 @@
         <v>1</v>
       </c>
       <c r="N108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O108" t="n">
         <v>1.2</v>
@@ -7944,12 +7944,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_02.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_28.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
@@ -7963,7 +7963,7 @@
       </c>
       <c r="M109" t="inlineStr"/>
       <c r="N109" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O109" t="n">
         <v>2</v>
@@ -8004,12 +8004,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_49.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
@@ -8037,7 +8037,7 @@
         <v>1</v>
       </c>
       <c r="N110" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O110" t="n">
         <v>1.2</v>
@@ -8082,12 +8082,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_49.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
@@ -8101,7 +8101,7 @@
       </c>
       <c r="M111" t="inlineStr"/>
       <c r="N111" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O111" t="n">
         <v>2</v>
@@ -8142,12 +8142,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_41.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
@@ -8175,7 +8175,7 @@
         <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O112" t="n">
         <v>1.2</v>
@@ -8220,12 +8220,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_41.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="H113" t="inlineStr"/>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="M113" t="inlineStr"/>
       <c r="N113" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O113" t="n">
         <v>2</v>
@@ -8280,12 +8280,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
@@ -8313,7 +8313,7 @@
         <v>1</v>
       </c>
       <c r="N114" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O114" t="n">
         <v>1.2</v>
@@ -8358,12 +8358,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="H115" t="inlineStr"/>
@@ -8377,7 +8377,7 @@
       </c>
       <c r="M115" t="inlineStr"/>
       <c r="N115" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O115" t="n">
         <v>2</v>
@@ -8418,12 +8418,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_02.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
@@ -8451,7 +8451,7 @@
         <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O116" t="n">
         <v>1.2</v>
@@ -8496,12 +8496,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_02.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
@@ -8515,7 +8515,7 @@
       </c>
       <c r="M117" t="inlineStr"/>
       <c r="N117" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O117" t="n">
         <v>2</v>
@@ -8556,12 +8556,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_28.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>stimuli/house/house_50.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
@@ -8589,7 +8589,7 @@
         <v>1</v>
       </c>
       <c r="N118" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O118" t="n">
         <v>1.2</v>
@@ -8634,12 +8634,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_28.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>stimuli/house/house_50.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
@@ -8653,7 +8653,7 @@
       </c>
       <c r="M119" t="inlineStr"/>
       <c r="N119" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O119" t="n">
         <v>2</v>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_14.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
@@ -8727,7 +8727,7 @@
         <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O120" t="n">
         <v>1.2</v>
@@ -8772,12 +8772,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_14.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
@@ -8791,7 +8791,7 @@
       </c>
       <c r="M121" t="inlineStr"/>
       <c r="N121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O121" t="n">
         <v>2</v>
@@ -8832,12 +8832,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_02.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="H122" t="inlineStr"/>
@@ -8865,7 +8865,7 @@
         <v>1</v>
       </c>
       <c r="N122" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O122" t="n">
         <v>1.2</v>
@@ -8910,12 +8910,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_02.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
@@ -8929,7 +8929,7 @@
       </c>
       <c r="M123" t="inlineStr"/>
       <c r="N123" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O123" t="n">
         <v>2</v>
@@ -8970,12 +8970,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_49.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
@@ -9003,7 +9003,7 @@
         <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O124" t="n">
         <v>1.2</v>
@@ -9048,12 +9048,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_49.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
@@ -9067,7 +9067,7 @@
       </c>
       <c r="M125" t="inlineStr"/>
       <c r="N125" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O125" t="n">
         <v>2</v>
@@ -9108,12 +9108,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>stimuli/house/house_50.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_28.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
@@ -9141,7 +9141,7 @@
         <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O126" t="n">
         <v>1.2</v>
@@ -9186,12 +9186,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>stimuli/house/house_50.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_28.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
@@ -9205,7 +9205,7 @@
       </c>
       <c r="M127" t="inlineStr"/>
       <c r="N127" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O127" t="n">
         <v>2</v>
@@ -9246,12 +9246,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_41.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="H128" t="inlineStr"/>
@@ -9279,7 +9279,7 @@
         <v>1</v>
       </c>
       <c r="N128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O128" t="n">
         <v>1.2</v>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_41.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
@@ -9343,7 +9343,7 @@
       </c>
       <c r="M129" t="inlineStr"/>
       <c r="N129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O129" t="n">
         <v>2</v>
@@ -9384,12 +9384,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_49.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_28.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
@@ -9417,7 +9417,7 @@
         <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O130" t="n">
         <v>1.2</v>
@@ -9462,12 +9462,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_49.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_28.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
@@ -9481,7 +9481,7 @@
       </c>
       <c r="M131" t="inlineStr"/>
       <c r="N131" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O131" t="n">
         <v>2</v>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_41.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
@@ -9555,7 +9555,7 @@
         <v>1</v>
       </c>
       <c r="N132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O132" t="n">
         <v>1.2</v>
@@ -9600,12 +9600,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_41.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
@@ -9619,7 +9619,7 @@
       </c>
       <c r="M133" t="inlineStr"/>
       <c r="N133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O133" t="n">
         <v>2</v>
@@ -9660,12 +9660,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>stimuli/house/house_50.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
@@ -9693,7 +9693,7 @@
         <v>0</v>
       </c>
       <c r="N134" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O134" t="n">
         <v>1.2</v>
@@ -9738,12 +9738,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>stimuli/house/house_50.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
@@ -9757,7 +9757,7 @@
       </c>
       <c r="M135" t="inlineStr"/>
       <c r="N135" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O135" t="n">
         <v>2</v>
@@ -9798,12 +9798,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_14.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="H136" t="inlineStr"/>
@@ -9831,7 +9831,7 @@
         <v>1</v>
       </c>
       <c r="N136" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O136" t="n">
         <v>1.2</v>
@@ -9876,12 +9876,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_14.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
@@ -9895,7 +9895,7 @@
       </c>
       <c r="M137" t="inlineStr"/>
       <c r="N137" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O137" t="n">
         <v>2</v>
@@ -9936,12 +9936,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_28.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_41.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="H138" t="inlineStr"/>
@@ -9969,7 +9969,7 @@
         <v>1</v>
       </c>
       <c r="N138" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O138" t="n">
         <v>1.2</v>
@@ -10014,12 +10014,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_28.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_41.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="H139" t="inlineStr"/>
@@ -10033,7 +10033,7 @@
       </c>
       <c r="M139" t="inlineStr"/>
       <c r="N139" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O139" t="n">
         <v>2</v>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="H140" t="inlineStr"/>
@@ -10107,7 +10107,7 @@
         <v>0</v>
       </c>
       <c r="N140" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O140" t="n">
         <v>1.2</v>
@@ -10152,12 +10152,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="H141" t="inlineStr"/>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="M141" t="inlineStr"/>
       <c r="N141" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O141" t="n">
         <v>2</v>
@@ -10212,12 +10212,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>stimuli/house/house_50.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_49.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="H142" t="inlineStr"/>
@@ -10245,7 +10245,7 @@
         <v>0</v>
       </c>
       <c r="N142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O142" t="n">
         <v>1.2</v>
@@ -10290,12 +10290,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>stimuli/house/house_50.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_49.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="H143" t="inlineStr"/>
@@ -10309,7 +10309,7 @@
       </c>
       <c r="M143" t="inlineStr"/>
       <c r="N143" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O143" t="n">
         <v>2</v>
@@ -10350,12 +10350,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="H144" t="inlineStr"/>
@@ -10383,7 +10383,7 @@
         <v>1</v>
       </c>
       <c r="N144" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O144" t="n">
         <v>1.2</v>
@@ -10428,12 +10428,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="H145" t="inlineStr"/>
@@ -10447,7 +10447,7 @@
       </c>
       <c r="M145" t="inlineStr"/>
       <c r="N145" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O145" t="n">
         <v>2</v>
@@ -10488,12 +10488,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_41.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="H146" t="inlineStr"/>
@@ -10521,7 +10521,7 @@
         <v>0</v>
       </c>
       <c r="N146" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O146" t="n">
         <v>1.2</v>
@@ -10566,12 +10566,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_41.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="H147" t="inlineStr"/>
@@ -10585,7 +10585,7 @@
       </c>
       <c r="M147" t="inlineStr"/>
       <c r="N147" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O147" t="n">
         <v>2</v>
@@ -10626,12 +10626,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_49.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="H148" t="inlineStr"/>
@@ -10659,7 +10659,7 @@
         <v>1</v>
       </c>
       <c r="N148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O148" t="n">
         <v>1.2</v>
@@ -10704,12 +10704,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_49.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="H149" t="inlineStr"/>
@@ -10723,7 +10723,7 @@
       </c>
       <c r="M149" t="inlineStr"/>
       <c r="N149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O149" t="n">
         <v>2</v>
@@ -10764,12 +10764,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_14.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_28.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="H150" t="inlineStr"/>
@@ -10797,7 +10797,7 @@
         <v>1</v>
       </c>
       <c r="N150" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O150" t="n">
         <v>1.2</v>
@@ -10842,12 +10842,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_14.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_28.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="H151" t="inlineStr"/>
@@ -10861,7 +10861,7 @@
       </c>
       <c r="M151" t="inlineStr"/>
       <c r="N151" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O151" t="n">
         <v>2</v>
@@ -10902,12 +10902,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_02.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="H152" t="inlineStr"/>
@@ -10935,7 +10935,7 @@
         <v>0</v>
       </c>
       <c r="N152" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O152" t="n">
         <v>1.2</v>
@@ -10980,12 +10980,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_02.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="H153" t="inlineStr"/>
@@ -10999,7 +10999,7 @@
       </c>
       <c r="M153" t="inlineStr"/>
       <c r="N153" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O153" t="n">
         <v>2</v>
@@ -11040,12 +11040,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_14.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="H154" t="inlineStr"/>
@@ -11073,7 +11073,7 @@
         <v>0</v>
       </c>
       <c r="N154" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O154" t="n">
         <v>1.2</v>
@@ -11118,12 +11118,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_14.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="H155" t="inlineStr"/>
@@ -11137,7 +11137,7 @@
       </c>
       <c r="M155" t="inlineStr"/>
       <c r="N155" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O155" t="n">
         <v>2</v>
@@ -11178,12 +11178,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_02.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_49.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="H156" t="inlineStr"/>
@@ -11211,7 +11211,7 @@
         <v>1</v>
       </c>
       <c r="N156" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O156" t="n">
         <v>1.2</v>
@@ -11256,12 +11256,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_02.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_49.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="H157" t="inlineStr"/>
@@ -11275,7 +11275,7 @@
       </c>
       <c r="M157" t="inlineStr"/>
       <c r="N157" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O157" t="n">
         <v>2</v>
@@ -11316,12 +11316,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_41.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="H158" t="inlineStr"/>
@@ -11349,7 +11349,7 @@
         <v>1</v>
       </c>
       <c r="N158" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O158" t="n">
         <v>1.2</v>
@@ -11394,12 +11394,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_41.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="H159" t="inlineStr"/>
@@ -11413,7 +11413,7 @@
       </c>
       <c r="M159" t="inlineStr"/>
       <c r="N159" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O159" t="n">
         <v>2</v>
@@ -11454,12 +11454,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="H160" t="inlineStr"/>
@@ -11487,7 +11487,7 @@
         <v>0</v>
       </c>
       <c r="N160" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O160" t="n">
         <v>1.2</v>
@@ -11532,12 +11532,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="H161" t="inlineStr"/>
@@ -11551,7 +11551,7 @@
       </c>
       <c r="M161" t="inlineStr"/>
       <c r="N161" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O161" t="n">
         <v>2</v>
@@ -11592,12 +11592,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_49.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_02.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="H162" t="inlineStr"/>
@@ -11625,7 +11625,7 @@
         <v>0</v>
       </c>
       <c r="N162" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O162" t="n">
         <v>1.2</v>
@@ -11670,12 +11670,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_49.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_02.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="H163" t="inlineStr"/>
@@ -11689,7 +11689,7 @@
       </c>
       <c r="M163" t="inlineStr"/>
       <c r="N163" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O163" t="n">
         <v>2</v>
@@ -11730,12 +11730,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_28.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_41.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="H164" t="inlineStr"/>
@@ -11763,7 +11763,7 @@
         <v>1</v>
       </c>
       <c r="N164" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O164" t="n">
         <v>1.2</v>
@@ -11808,12 +11808,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_28.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_41.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="H165" t="inlineStr"/>
@@ -11827,7 +11827,7 @@
       </c>
       <c r="M165" t="inlineStr"/>
       <c r="N165" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O165" t="n">
         <v>2</v>
@@ -11868,12 +11868,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="H166" t="inlineStr"/>
@@ -11901,7 +11901,7 @@
         <v>1</v>
       </c>
       <c r="N166" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O166" t="n">
         <v>1.2</v>
@@ -11946,12 +11946,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="H167" t="inlineStr"/>
@@ -11965,7 +11965,7 @@
       </c>
       <c r="M167" t="inlineStr"/>
       <c r="N167" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O167" t="n">
         <v>2</v>
@@ -12006,12 +12006,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>stimuli/house/house_50.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="H168" t="inlineStr"/>
@@ -12039,7 +12039,7 @@
         <v>0</v>
       </c>
       <c r="N168" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O168" t="n">
         <v>1.2</v>
@@ -12084,12 +12084,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>stimuli/house/house_50.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="H169" t="inlineStr"/>
@@ -12103,7 +12103,7 @@
       </c>
       <c r="M169" t="inlineStr"/>
       <c r="N169" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O169" t="n">
         <v>2</v>
@@ -12144,12 +12144,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_14.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="H170" t="inlineStr"/>
@@ -12177,7 +12177,7 @@
         <v>1</v>
       </c>
       <c r="N170" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O170" t="n">
         <v>1.2</v>
@@ -12222,12 +12222,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_14.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="H171" t="inlineStr"/>
@@ -12241,7 +12241,7 @@
       </c>
       <c r="M171" t="inlineStr"/>
       <c r="N171" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O171" t="n">
         <v>2</v>
@@ -12282,12 +12282,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_41.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="H172" t="inlineStr"/>
@@ -12315,7 +12315,7 @@
         <v>0</v>
       </c>
       <c r="N172" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O172" t="n">
         <v>1.2</v>
@@ -12360,12 +12360,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_41.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="H173" t="inlineStr"/>
@@ -12379,7 +12379,7 @@
       </c>
       <c r="M173" t="inlineStr"/>
       <c r="N173" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O173" t="n">
         <v>2</v>
@@ -12420,12 +12420,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_49.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="H174" t="inlineStr"/>
@@ -12453,7 +12453,7 @@
         <v>1</v>
       </c>
       <c r="N174" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O174" t="n">
         <v>1.2</v>
@@ -12498,12 +12498,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_49.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="H175" t="inlineStr"/>
@@ -12517,7 +12517,7 @@
       </c>
       <c r="M175" t="inlineStr"/>
       <c r="N175" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O175" t="n">
         <v>2</v>
@@ -12558,12 +12558,12 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_28.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="H176" t="inlineStr"/>
@@ -12591,7 +12591,7 @@
         <v>0</v>
       </c>
       <c r="N176" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O176" t="n">
         <v>1.2</v>
@@ -12636,12 +12636,12 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_28.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="H177" t="inlineStr"/>
@@ -12655,7 +12655,7 @@
       </c>
       <c r="M177" t="inlineStr"/>
       <c r="N177" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O177" t="n">
         <v>2</v>
@@ -12696,12 +12696,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_02.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="H178" t="inlineStr"/>
@@ -12729,7 +12729,7 @@
         <v>1</v>
       </c>
       <c r="N178" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O178" t="n">
         <v>1.2</v>
@@ -12774,12 +12774,12 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_02.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="H179" t="inlineStr"/>
@@ -12793,7 +12793,7 @@
       </c>
       <c r="M179" t="inlineStr"/>
       <c r="N179" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O179" t="n">
         <v>2</v>
@@ -12834,12 +12834,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>stimuli/house/house_50.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_28.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="H180" t="inlineStr"/>
@@ -12867,7 +12867,7 @@
         <v>0</v>
       </c>
       <c r="N180" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O180" t="n">
         <v>1.2</v>
@@ -12912,12 +12912,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>stimuli/house/house_50.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_28.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="H181" t="inlineStr"/>
@@ -12931,7 +12931,7 @@
       </c>
       <c r="M181" t="inlineStr"/>
       <c r="N181" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O181" t="n">
         <v>2</v>
@@ -12972,12 +12972,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_14.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="H182" t="inlineStr"/>
@@ -13005,7 +13005,7 @@
         <v>0</v>
       </c>
       <c r="N182" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O182" t="n">
         <v>1.2</v>
@@ -13050,12 +13050,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_14.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="H183" t="inlineStr"/>
@@ -13069,7 +13069,7 @@
       </c>
       <c r="M183" t="inlineStr"/>
       <c r="N183" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O183" t="n">
         <v>2</v>
@@ -13110,12 +13110,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="H184" t="inlineStr"/>
@@ -13143,7 +13143,7 @@
         <v>1</v>
       </c>
       <c r="N184" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O184" t="n">
         <v>1.2</v>
@@ -13188,12 +13188,12 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="H185" t="inlineStr"/>
@@ -13207,7 +13207,7 @@
       </c>
       <c r="M185" t="inlineStr"/>
       <c r="N185" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O185" t="n">
         <v>2</v>
@@ -13248,12 +13248,12 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>stimuli/house/house_50.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="H186" t="inlineStr"/>
@@ -13281,7 +13281,7 @@
         <v>0</v>
       </c>
       <c r="N186" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O186" t="n">
         <v>1.2</v>
@@ -13326,12 +13326,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>stimuli/house/house_50.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="H187" t="inlineStr"/>
@@ -13345,7 +13345,7 @@
       </c>
       <c r="M187" t="inlineStr"/>
       <c r="N187" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O187" t="n">
         <v>2</v>
@@ -13386,12 +13386,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_28.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_49.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="H188" t="inlineStr"/>
@@ -13419,7 +13419,7 @@
         <v>1</v>
       </c>
       <c r="N188" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O188" t="n">
         <v>1.2</v>
@@ -13464,12 +13464,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_28.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_49.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="H189" t="inlineStr"/>
@@ -13483,7 +13483,7 @@
       </c>
       <c r="M189" t="inlineStr"/>
       <c r="N189" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O189" t="n">
         <v>2</v>
@@ -13524,12 +13524,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_14.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="H190" t="inlineStr"/>
@@ -13557,7 +13557,7 @@
         <v>1</v>
       </c>
       <c r="N190" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O190" t="n">
         <v>1.2</v>
@@ -13602,12 +13602,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_14.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="H191" t="inlineStr"/>
@@ -13621,7 +13621,7 @@
       </c>
       <c r="M191" t="inlineStr"/>
       <c r="N191" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O191" t="n">
         <v>2</v>
@@ -13662,12 +13662,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_41.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="H192" t="inlineStr"/>
@@ -13695,7 +13695,7 @@
         <v>0</v>
       </c>
       <c r="N192" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O192" t="n">
         <v>1.2</v>
@@ -13740,12 +13740,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_41.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="H193" t="inlineStr"/>
@@ -13759,7 +13759,7 @@
       </c>
       <c r="M193" t="inlineStr"/>
       <c r="N193" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O193" t="n">
         <v>2</v>
@@ -13800,12 +13800,12 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_02.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="H194" t="inlineStr"/>
@@ -13833,7 +13833,7 @@
         <v>0</v>
       </c>
       <c r="N194" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O194" t="n">
         <v>1.2</v>
@@ -13878,12 +13878,12 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_02.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="H195" t="inlineStr"/>
@@ -13897,7 +13897,7 @@
       </c>
       <c r="M195" t="inlineStr"/>
       <c r="N195" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O195" t="n">
         <v>2</v>
@@ -13938,12 +13938,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_14.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_28.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="H196" t="inlineStr"/>
@@ -13971,7 +13971,7 @@
         <v>1</v>
       </c>
       <c r="N196" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O196" t="n">
         <v>1.2</v>
@@ -14016,12 +14016,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_14.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_28.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="H197" t="inlineStr"/>
@@ -14035,7 +14035,7 @@
       </c>
       <c r="M197" t="inlineStr"/>
       <c r="N197" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O197" t="n">
         <v>2</v>
@@ -14076,12 +14076,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_49.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>stimuli/house/house_50.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="H198" t="inlineStr"/>
@@ -14109,7 +14109,7 @@
         <v>1</v>
       </c>
       <c r="N198" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O198" t="n">
         <v>1.2</v>
@@ -14154,12 +14154,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_49.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>stimuli/house/house_50.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="H199" t="inlineStr"/>
@@ -14173,7 +14173,7 @@
       </c>
       <c r="M199" t="inlineStr"/>
       <c r="N199" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O199" t="n">
         <v>2</v>
@@ -14214,12 +14214,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="H200" t="inlineStr"/>
@@ -14247,7 +14247,7 @@
         <v>0</v>
       </c>
       <c r="N200" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O200" t="n">
         <v>1.2</v>
@@ -14292,12 +14292,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="H201" t="inlineStr"/>
@@ -14311,7 +14311,7 @@
       </c>
       <c r="M201" t="inlineStr"/>
       <c r="N201" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O201" t="n">
         <v>2</v>
@@ -14352,12 +14352,12 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_28.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="H202" t="inlineStr"/>
@@ -14385,7 +14385,7 @@
         <v>1</v>
       </c>
       <c r="N202" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O202" t="n">
         <v>1.2</v>
@@ -14430,12 +14430,12 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_28.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="H203" t="inlineStr"/>
@@ -14449,7 +14449,7 @@
       </c>
       <c r="M203" t="inlineStr"/>
       <c r="N203" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O203" t="n">
         <v>2</v>
@@ -14490,12 +14490,12 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_41.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="H204" t="inlineStr"/>
@@ -14523,7 +14523,7 @@
         <v>0</v>
       </c>
       <c r="N204" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O204" t="n">
         <v>1.2</v>
@@ -14568,12 +14568,12 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_41.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="H205" t="inlineStr"/>
@@ -14587,7 +14587,7 @@
       </c>
       <c r="M205" t="inlineStr"/>
       <c r="N205" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O205" t="n">
         <v>2</v>
@@ -14628,12 +14628,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_49.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="H206" t="inlineStr"/>
@@ -14661,7 +14661,7 @@
         <v>0</v>
       </c>
       <c r="N206" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O206" t="n">
         <v>1.2</v>
@@ -14706,12 +14706,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_49.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="H207" t="inlineStr"/>
@@ -14725,7 +14725,7 @@
       </c>
       <c r="M207" t="inlineStr"/>
       <c r="N207" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O207" t="n">
         <v>2</v>
@@ -14766,12 +14766,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>stimuli/house/house_50.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="H208" t="inlineStr"/>
@@ -14799,7 +14799,7 @@
         <v>1</v>
       </c>
       <c r="N208" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O208" t="n">
         <v>1.2</v>
@@ -14844,12 +14844,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>stimuli/house/house_50.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="H209" t="inlineStr"/>
@@ -14863,7 +14863,7 @@
       </c>
       <c r="M209" t="inlineStr"/>
       <c r="N209" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O209" t="n">
         <v>2</v>
@@ -14904,12 +14904,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_28.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_41.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="H210" t="inlineStr"/>
@@ -14937,7 +14937,7 @@
         <v>1</v>
       </c>
       <c r="N210" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O210" t="n">
         <v>1.2</v>
@@ -14982,12 +14982,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_28.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_41.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="H211" t="inlineStr"/>
@@ -15001,7 +15001,7 @@
       </c>
       <c r="M211" t="inlineStr"/>
       <c r="N211" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O211" t="n">
         <v>2</v>
@@ -15042,12 +15042,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>stimuli/house/house_50.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="H212" t="inlineStr"/>
@@ -15075,7 +15075,7 @@
         <v>0</v>
       </c>
       <c r="N212" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O212" t="n">
         <v>1.2</v>
@@ -15120,12 +15120,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>stimuli/house/house_50.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="H213" t="inlineStr"/>
@@ -15139,7 +15139,7 @@
       </c>
       <c r="M213" t="inlineStr"/>
       <c r="N213" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O213" t="n">
         <v>2</v>
@@ -15180,12 +15180,12 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="H214" t="inlineStr"/>
@@ -15213,7 +15213,7 @@
         <v>1</v>
       </c>
       <c r="N214" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O214" t="n">
         <v>1.2</v>
@@ -15258,12 +15258,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="H215" t="inlineStr"/>
@@ -15277,7 +15277,7 @@
       </c>
       <c r="M215" t="inlineStr"/>
       <c r="N215" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O215" t="n">
         <v>2</v>
@@ -15318,12 +15318,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_49.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_02.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="H216" t="inlineStr"/>
@@ -15351,7 +15351,7 @@
         <v>0</v>
       </c>
       <c r="N216" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O216" t="n">
         <v>1.2</v>
@@ -15396,12 +15396,12 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_49.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_02.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="H217" t="inlineStr"/>
@@ -15415,7 +15415,7 @@
       </c>
       <c r="M217" t="inlineStr"/>
       <c r="N217" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O217" t="n">
         <v>2</v>
@@ -15456,12 +15456,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_14.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="H218" t="inlineStr"/>
@@ -15489,7 +15489,7 @@
         <v>1</v>
       </c>
       <c r="N218" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O218" t="n">
         <v>1.2</v>
@@ -15534,12 +15534,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_14.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="H219" t="inlineStr"/>
@@ -15553,7 +15553,7 @@
       </c>
       <c r="M219" t="inlineStr"/>
       <c r="N219" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O219" t="n">
         <v>2</v>
@@ -15594,12 +15594,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_49.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="H220" t="inlineStr"/>
@@ -15627,7 +15627,7 @@
         <v>0</v>
       </c>
       <c r="N220" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O220" t="n">
         <v>1.2</v>
@@ -15672,12 +15672,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_49.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="H221" t="inlineStr"/>
@@ -15691,7 +15691,7 @@
       </c>
       <c r="M221" t="inlineStr"/>
       <c r="N221" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O221" t="n">
         <v>2</v>
@@ -15732,12 +15732,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_41.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="H222" t="inlineStr"/>
@@ -15765,7 +15765,7 @@
         <v>0</v>
       </c>
       <c r="N222" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O222" t="n">
         <v>1.2</v>
@@ -15810,12 +15810,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_41.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="H223" t="inlineStr"/>
@@ -15829,7 +15829,7 @@
       </c>
       <c r="M223" t="inlineStr"/>
       <c r="N223" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O223" t="n">
         <v>2</v>
@@ -15870,12 +15870,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_02.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_28.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="H224" t="inlineStr"/>
@@ -15903,7 +15903,7 @@
         <v>1</v>
       </c>
       <c r="N224" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O224" t="n">
         <v>1.2</v>
@@ -15948,12 +15948,12 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_02.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_28.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="H225" t="inlineStr"/>
@@ -15967,7 +15967,7 @@
       </c>
       <c r="M225" t="inlineStr"/>
       <c r="N225" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O225" t="n">
         <v>2</v>
@@ -16008,12 +16008,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="H226" t="inlineStr"/>
@@ -16041,7 +16041,7 @@
         <v>1</v>
       </c>
       <c r="N226" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O226" t="n">
         <v>1.2</v>
@@ -16086,12 +16086,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="H227" t="inlineStr"/>
@@ -16105,7 +16105,7 @@
       </c>
       <c r="M227" t="inlineStr"/>
       <c r="N227" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O227" t="n">
         <v>2</v>
@@ -16146,12 +16146,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>stimuli/house/house_50.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_28.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="H228" t="inlineStr"/>
@@ -16179,7 +16179,7 @@
         <v>0</v>
       </c>
       <c r="N228" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O228" t="n">
         <v>1.2</v>
@@ -16224,12 +16224,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>stimuli/house/house_50.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_28.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="H229" t="inlineStr"/>
@@ -16243,7 +16243,7 @@
       </c>
       <c r="M229" t="inlineStr"/>
       <c r="N229" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O229" t="n">
         <v>2</v>
@@ -16284,12 +16284,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_14.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="H230" t="inlineStr"/>
@@ -16317,7 +16317,7 @@
         <v>0</v>
       </c>
       <c r="N230" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O230" t="n">
         <v>1.2</v>
@@ -16362,12 +16362,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_14.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="H231" t="inlineStr"/>
@@ -16381,7 +16381,7 @@
       </c>
       <c r="M231" t="inlineStr"/>
       <c r="N231" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O231" t="n">
         <v>2</v>
@@ -16422,12 +16422,12 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_02.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="H232" t="inlineStr"/>
@@ -16455,7 +16455,7 @@
         <v>1</v>
       </c>
       <c r="N232" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O232" t="n">
         <v>1.2</v>
@@ -16500,12 +16500,12 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_02.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="H233" t="inlineStr"/>
@@ -16519,7 +16519,7 @@
       </c>
       <c r="M233" t="inlineStr"/>
       <c r="N233" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O233" t="n">
         <v>2</v>
@@ -16560,12 +16560,12 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_28.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_14.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="H234" t="inlineStr"/>
@@ -16593,7 +16593,7 @@
         <v>0</v>
       </c>
       <c r="N234" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O234" t="n">
         <v>1.2</v>
@@ -16638,12 +16638,12 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_28.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_14.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="H235" t="inlineStr"/>
@@ -16657,7 +16657,7 @@
       </c>
       <c r="M235" t="inlineStr"/>
       <c r="N235" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O235" t="n">
         <v>2</v>
@@ -16698,12 +16698,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_02.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="H236" t="inlineStr"/>
@@ -16731,7 +16731,7 @@
         <v>1</v>
       </c>
       <c r="N236" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O236" t="n">
         <v>1.2</v>
@@ -16776,12 +16776,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_02.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_23.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="H237" t="inlineStr"/>
@@ -16795,7 +16795,7 @@
       </c>
       <c r="M237" t="inlineStr"/>
       <c r="N237" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O237" t="n">
         <v>2</v>
@@ -16836,12 +16836,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>stimuli/house/house_50.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_49.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="H238" t="inlineStr"/>
@@ -16869,7 +16869,7 @@
         <v>0</v>
       </c>
       <c r="N238" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O238" t="n">
         <v>1.2</v>
@@ -16914,12 +16914,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>stimuli/house/house_50.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_49.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="H239" t="inlineStr"/>
@@ -16933,7 +16933,7 @@
       </c>
       <c r="M239" t="inlineStr"/>
       <c r="N239" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O239" t="n">
         <v>2</v>
@@ -16974,12 +16974,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="H240" t="inlineStr"/>
@@ -17007,7 +17007,7 @@
         <v>1</v>
       </c>
       <c r="N240" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O240" t="n">
         <v>1.2</v>
@@ -17052,12 +17052,12 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="H241" t="inlineStr"/>
@@ -17071,7 +17071,7 @@
       </c>
       <c r="M241" t="inlineStr"/>
       <c r="N241" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O241" t="n">
         <v>2</v>

--- a/psychopy_exp_files/sequences/retrieval_block1_fixed-middle-10_48.xlsx
+++ b/psychopy_exp_files/sequences/retrieval_block1_fixed-middle-10_48.xlsx
@@ -552,12 +552,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -630,12 +630,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -690,12 +690,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -768,12 +768,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -966,12 +966,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -1146,10 +1146,10 @@
         <v>0.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="R10" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -1242,12 +1242,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -1275,7 +1275,7 @@
         <v>1</v>
       </c>
       <c r="N12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O12" t="n">
         <v>1.2</v>
@@ -1284,10 +1284,10 @@
         <v>0.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.35</v>
+        <v>0.71</v>
       </c>
       <c r="R12" t="n">
-        <v>2.14</v>
+        <v>1.81</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1320,12 +1320,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -1334,12 +1334,12 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O13" t="n">
         <v>2</v>
@@ -1385,20 +1385,20 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>left</t>
@@ -1410,10 +1410,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O14" t="n">
         <v>1.2</v>
@@ -1422,10 +1422,10 @@
         <v>0.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="R14" t="n">
-        <v>2.21</v>
+        <v>2.04</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -1472,12 +1472,12 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O15" t="n">
         <v>2</v>
@@ -1518,25 +1518,25 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>stimuli/jacket/jacket_27.jpg</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_06.jpg</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>left</t>
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>5</v>
@@ -1560,10 +1560,10 @@
         <v>0.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.71</v>
+        <v>0.3</v>
       </c>
       <c r="R16" t="n">
-        <v>1.81</v>
+        <v>1.99</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -1596,12 +1596,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>stimuli/jacket/jacket_27.jpg</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_06.jpg</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -1698,10 +1698,10 @@
         <v>0.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.6</v>
+        <v>0.46</v>
       </c>
       <c r="R18" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -1794,40 +1794,40 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O20" t="n">
         <v>1.2</v>
@@ -1836,10 +1836,10 @@
         <v>0.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="R20" t="n">
-        <v>2.16</v>
+        <v>1.91</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
@@ -1886,12 +1886,12 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O21" t="n">
         <v>2</v>
@@ -1932,40 +1932,40 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O22" t="n">
         <v>1.2</v>
@@ -1974,10 +1974,10 @@
         <v>0.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.44</v>
+        <v>0.38</v>
       </c>
       <c r="R22" t="n">
-        <v>1.89</v>
+        <v>2.07</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2010,12 +2010,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
@@ -2024,12 +2024,12 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O23" t="n">
         <v>2</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
+          <t>stimuli/hand/hand_10.jpg</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
           <t>stimuli/jacket/jacket_27.jpg</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -2103,7 +2103,7 @@
         <v>1</v>
       </c>
       <c r="N24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O24" t="n">
         <v>1.2</v>
@@ -2112,10 +2112,10 @@
         <v>0.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.68</v>
+        <v>0.47</v>
       </c>
       <c r="R24" t="n">
-        <v>1.81</v>
+        <v>2.2</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -2148,12 +2148,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
+          <t>stimuli/hand/hand_10.jpg</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
           <t>stimuli/jacket/jacket_27.jpg</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -2162,12 +2162,12 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O25" t="n">
         <v>2</v>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
+          <t>stimuli/house/house_35.jpg</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_27.jpg</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
@@ -2229,16 +2229,16 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N26" t="n">
         <v>5</v>
@@ -2250,10 +2250,10 @@
         <v>0.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.37</v>
+        <v>0.71</v>
       </c>
       <c r="R26" t="n">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -2286,12 +2286,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
+          <t>stimuli/house/house_35.jpg</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_27.jpg</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
@@ -2346,12 +2346,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
@@ -2367,19 +2367,19 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O28" t="n">
         <v>1.2</v>
@@ -2388,10 +2388,10 @@
         <v>0.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.67</v>
+        <v>0.39</v>
       </c>
       <c r="R28" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -2424,12 +2424,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
@@ -2438,12 +2438,12 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O29" t="n">
         <v>2</v>
@@ -2484,12 +2484,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
@@ -2505,19 +2505,19 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O30" t="n">
         <v>1.2</v>
@@ -2526,10 +2526,10 @@
         <v>0.2</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.35</v>
+        <v>0.58</v>
       </c>
       <c r="R30" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -2562,12 +2562,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
@@ -2576,12 +2576,12 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O31" t="n">
         <v>2</v>
@@ -2622,12 +2622,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
@@ -2643,19 +2643,19 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O32" t="n">
         <v>1.2</v>
@@ -2664,10 +2664,10 @@
         <v>0.2</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="R32" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -2700,12 +2700,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
@@ -2714,12 +2714,12 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O33" t="n">
         <v>2</v>
@@ -2760,40 +2760,40 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M34" t="n">
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O34" t="n">
         <v>1.2</v>
@@ -2802,10 +2802,10 @@
         <v>0.2</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.6</v>
+        <v>0.33</v>
       </c>
       <c r="R34" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -2838,12 +2838,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
@@ -2852,12 +2852,12 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O35" t="n">
         <v>2</v>
@@ -2898,7 +2898,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2931,7 +2931,7 @@
         <v>1</v>
       </c>
       <c r="N36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O36" t="n">
         <v>1.2</v>
@@ -2940,10 +2940,10 @@
         <v>0.2</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.46</v>
+        <v>0.55</v>
       </c>
       <c r="R36" t="n">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -2976,7 +2976,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2990,12 +2990,12 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O37" t="n">
         <v>2</v>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -3057,19 +3057,19 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O38" t="n">
         <v>1.2</v>
@@ -3078,10 +3078,10 @@
         <v>0.2</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.36</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="R38" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
@@ -3128,12 +3128,12 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O39" t="n">
         <v>2</v>
@@ -3174,25 +3174,25 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="K40" t="inlineStr">
         <is>
           <t>right</t>
@@ -3204,10 +3204,10 @@
         </is>
       </c>
       <c r="M40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O40" t="n">
         <v>1.2</v>
@@ -3216,10 +3216,10 @@
         <v>0.2</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.63</v>
+        <v>0.3</v>
       </c>
       <c r="R40" t="n">
-        <v>2.13</v>
+        <v>1.9</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -3252,12 +3252,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -3266,12 +3266,12 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O41" t="n">
         <v>2</v>
@@ -3312,25 +3312,25 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="K42" t="inlineStr">
         <is>
           <t>left</t>
@@ -3342,10 +3342,10 @@
         </is>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N42" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O42" t="n">
         <v>1.2</v>
@@ -3354,10 +3354,10 @@
         <v>0.2</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.51</v>
+        <v>0.7</v>
       </c>
       <c r="R42" t="n">
-        <v>1.96</v>
+        <v>1.78</v>
       </c>
       <c r="S42" t="n">
         <v>2</v>
@@ -3390,12 +3390,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
@@ -3404,12 +3404,12 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O43" t="n">
         <v>2</v>
@@ -3450,12 +3450,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
@@ -3471,16 +3471,16 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
         <v>3</v>
@@ -3492,10 +3492,10 @@
         <v>0.2</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.41</v>
+        <v>0.37</v>
       </c>
       <c r="R44" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="S44" t="n">
         <v>2</v>
@@ -3528,12 +3528,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
@@ -3588,12 +3588,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
@@ -3609,16 +3609,16 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
         <v>4</v>
@@ -3630,10 +3630,10 @@
         <v>0.2</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.73</v>
+        <v>0.39</v>
       </c>
       <c r="R46" t="n">
-        <v>1.81</v>
+        <v>2.19</v>
       </c>
       <c r="S46" t="n">
         <v>2</v>
@@ -3666,12 +3666,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
@@ -3726,25 +3726,25 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
       <c r="K48" t="inlineStr">
         <is>
           <t>right</t>
@@ -3756,10 +3756,10 @@
         </is>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N48" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O48" t="n">
         <v>1.2</v>
@@ -3768,10 +3768,10 @@
         <v>0.2</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.73</v>
+        <v>0.59</v>
       </c>
       <c r="R48" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="S48" t="n">
         <v>2</v>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
@@ -3818,12 +3818,12 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O49" t="n">
         <v>2</v>
@@ -3864,40 +3864,40 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M50" t="n">
         <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O50" t="n">
         <v>1.2</v>
@@ -3906,7 +3906,7 @@
         <v>0.2</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.32</v>
+        <v>0.62</v>
       </c>
       <c r="R50" t="n">
         <v>1.85</v>
@@ -3942,12 +3942,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
@@ -3956,12 +3956,12 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O51" t="n">
         <v>2</v>
@@ -4002,40 +4002,40 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M52" t="n">
         <v>1</v>
       </c>
       <c r="N52" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O52" t="n">
         <v>1.2</v>
@@ -4044,10 +4044,10 @@
         <v>0.2</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.37</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R52" t="n">
-        <v>1.97</v>
+        <v>2.23</v>
       </c>
       <c r="S52" t="n">
         <v>2</v>
@@ -4080,12 +4080,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
@@ -4094,12 +4094,12 @@
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O53" t="n">
         <v>2</v>
@@ -4140,40 +4140,40 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
+          <t>stimuli/dog/dog_08.jpg</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_19.jpg</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M54" t="n">
         <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O54" t="n">
         <v>1.2</v>
@@ -4182,10 +4182,10 @@
         <v>0.2</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.58</v>
+        <v>0.26</v>
       </c>
       <c r="R54" t="n">
-        <v>1.86</v>
+        <v>2.06</v>
       </c>
       <c r="S54" t="n">
         <v>2</v>
@@ -4218,12 +4218,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
+          <t>stimuli/dog/dog_08.jpg</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_19.jpg</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
@@ -4232,12 +4232,12 @@
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O55" t="n">
         <v>2</v>
@@ -4278,40 +4278,40 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M56" t="n">
         <v>1</v>
       </c>
       <c r="N56" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O56" t="n">
         <v>1.2</v>
@@ -4320,10 +4320,10 @@
         <v>0.2</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.61</v>
+        <v>0.75</v>
       </c>
       <c r="R56" t="n">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="S56" t="n">
         <v>2</v>
@@ -4356,12 +4356,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
@@ -4370,12 +4370,12 @@
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O57" t="n">
         <v>2</v>
@@ -4416,25 +4416,25 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="K58" t="inlineStr">
         <is>
           <t>right</t>
@@ -4446,10 +4446,10 @@
         </is>
       </c>
       <c r="M58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O58" t="n">
         <v>1.2</v>
@@ -4458,10 +4458,10 @@
         <v>0.2</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="R58" t="n">
-        <v>1.9</v>
+        <v>2.14</v>
       </c>
       <c r="S58" t="n">
         <v>2</v>
@@ -4494,12 +4494,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
@@ -4508,12 +4508,12 @@
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O59" t="n">
         <v>2</v>
@@ -4554,12 +4554,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
@@ -4575,19 +4575,19 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O60" t="n">
         <v>1.2</v>
@@ -4596,10 +4596,10 @@
         <v>0.2</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.66</v>
+        <v>0.5</v>
       </c>
       <c r="R60" t="n">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="S60" t="n">
         <v>2</v>
@@ -4632,12 +4632,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
@@ -4646,12 +4646,12 @@
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O61" t="n">
         <v>2</v>
@@ -4692,12 +4692,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
@@ -4713,16 +4713,16 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N62" t="n">
         <v>5</v>
@@ -4734,7 +4734,7 @@
         <v>0.2</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="R62" t="n">
         <v>2.23</v>
@@ -4770,12 +4770,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
@@ -4830,25 +4830,25 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
       <c r="K64" t="inlineStr">
         <is>
           <t>left</t>
@@ -4860,10 +4860,10 @@
         </is>
       </c>
       <c r="M64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O64" t="n">
         <v>1.2</v>
@@ -4872,10 +4872,10 @@
         <v>0.2</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.67</v>
+        <v>0.38</v>
       </c>
       <c r="R64" t="n">
-        <v>1.92</v>
+        <v>2.22</v>
       </c>
       <c r="S64" t="n">
         <v>2</v>
@@ -4908,12 +4908,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
@@ -4922,12 +4922,12 @@
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O65" t="n">
         <v>2</v>
@@ -4968,25 +4968,25 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
       <c r="K66" t="inlineStr">
         <is>
           <t>left</t>
@@ -4998,10 +4998,10 @@
         </is>
       </c>
       <c r="M66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O66" t="n">
         <v>1.2</v>
@@ -5010,10 +5010,10 @@
         <v>0.2</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.29</v>
+        <v>0.75</v>
       </c>
       <c r="R66" t="n">
-        <v>1.95</v>
+        <v>2.09</v>
       </c>
       <c r="S66" t="n">
         <v>2</v>
@@ -5046,12 +5046,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
@@ -5060,12 +5060,12 @@
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O67" t="n">
         <v>2</v>
@@ -5106,25 +5106,25 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="K68" t="inlineStr">
         <is>
           <t>left</t>
@@ -5136,7 +5136,7 @@
         </is>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N68" t="n">
         <v>5</v>
@@ -5148,10 +5148,10 @@
         <v>0.2</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
       <c r="R68" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="S68" t="n">
         <v>2</v>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
@@ -5244,12 +5244,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
@@ -5277,7 +5277,7 @@
         <v>1</v>
       </c>
       <c r="N70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O70" t="n">
         <v>1.2</v>
@@ -5286,10 +5286,10 @@
         <v>0.2</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="R70" t="n">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="S70" t="n">
         <v>2</v>
@@ -5322,12 +5322,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
@@ -5336,12 +5336,12 @@
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O71" t="n">
         <v>2</v>
@@ -5382,12 +5382,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
@@ -5424,10 +5424,10 @@
         <v>0.2</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.58</v>
+        <v>0.33</v>
       </c>
       <c r="R72" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="S72" t="n">
         <v>2</v>
@@ -5460,12 +5460,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
@@ -5520,25 +5520,25 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
       <c r="K74" t="inlineStr">
         <is>
           <t>left</t>
@@ -5550,10 +5550,10 @@
         </is>
       </c>
       <c r="M74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O74" t="n">
         <v>1.2</v>
@@ -5562,10 +5562,10 @@
         <v>0.2</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.26</v>
+        <v>0.67</v>
       </c>
       <c r="R74" t="n">
-        <v>1.93</v>
+        <v>1.78</v>
       </c>
       <c r="S74" t="n">
         <v>2</v>
@@ -5598,12 +5598,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
@@ -5612,12 +5612,12 @@
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O75" t="n">
         <v>2</v>
@@ -5658,25 +5658,25 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
       <c r="K76" t="inlineStr">
         <is>
           <t>right</t>
@@ -5688,10 +5688,10 @@
         </is>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N76" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O76" t="n">
         <v>1.2</v>
@@ -5700,10 +5700,10 @@
         <v>0.2</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.54</v>
+        <v>0.65</v>
       </c>
       <c r="R76" t="n">
-        <v>2.11</v>
+        <v>1.82</v>
       </c>
       <c r="S76" t="n">
         <v>2</v>
@@ -5736,12 +5736,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
@@ -5750,12 +5750,12 @@
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O77" t="n">
         <v>2</v>
@@ -5796,25 +5796,25 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="K78" t="inlineStr">
         <is>
           <t>left</t>
@@ -5826,10 +5826,10 @@
         </is>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N78" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O78" t="n">
         <v>1.2</v>
@@ -5838,10 +5838,10 @@
         <v>0.2</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.26</v>
+        <v>0.35</v>
       </c>
       <c r="R78" t="n">
-        <v>1.75</v>
+        <v>1.96</v>
       </c>
       <c r="S78" t="n">
         <v>2</v>
@@ -5874,12 +5874,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
@@ -5888,12 +5888,12 @@
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O79" t="n">
         <v>2</v>
@@ -5934,25 +5934,25 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="K80" t="inlineStr">
         <is>
           <t>right</t>
@@ -5964,10 +5964,10 @@
         </is>
       </c>
       <c r="M80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O80" t="n">
         <v>1.2</v>
@@ -5976,10 +5976,10 @@
         <v>0.2</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.66</v>
+        <v>0.37</v>
       </c>
       <c r="R80" t="n">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="S80" t="n">
         <v>2</v>
@@ -6012,12 +6012,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
@@ -6026,12 +6026,12 @@
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O81" t="n">
         <v>2</v>
@@ -6072,25 +6072,25 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="K82" t="inlineStr">
         <is>
           <t>right</t>
@@ -6102,10 +6102,10 @@
         </is>
       </c>
       <c r="M82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O82" t="n">
         <v>1.2</v>
@@ -6114,10 +6114,10 @@
         <v>0.2</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.74</v>
+        <v>0.68</v>
       </c>
       <c r="R82" t="n">
-        <v>1.98</v>
+        <v>2.11</v>
       </c>
       <c r="S82" t="n">
         <v>3</v>
@@ -6150,12 +6150,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
@@ -6164,12 +6164,12 @@
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O83" t="n">
         <v>2</v>
@@ -6210,25 +6210,25 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
       <c r="K84" t="inlineStr">
         <is>
           <t>right</t>
@@ -6240,10 +6240,10 @@
         </is>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N84" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O84" t="n">
         <v>1.2</v>
@@ -6252,10 +6252,10 @@
         <v>0.2</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.41</v>
+        <v>0.53</v>
       </c>
       <c r="R84" t="n">
-        <v>1.77</v>
+        <v>2.08</v>
       </c>
       <c r="S84" t="n">
         <v>3</v>
@@ -6288,12 +6288,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
@@ -6302,12 +6302,12 @@
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M85" t="inlineStr"/>
       <c r="N85" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O85" t="n">
         <v>2</v>
@@ -6348,25 +6348,25 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="K86" t="inlineStr">
         <is>
           <t>left</t>
@@ -6378,10 +6378,10 @@
         </is>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O86" t="n">
         <v>1.2</v>
@@ -6390,10 +6390,10 @@
         <v>0.2</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.5</v>
+        <v>0.34</v>
       </c>
       <c r="R86" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="S86" t="n">
         <v>3</v>
@@ -6426,12 +6426,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
@@ -6440,12 +6440,12 @@
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M87" t="inlineStr"/>
       <c r="N87" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O87" t="n">
         <v>2</v>
@@ -6486,25 +6486,25 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
       <c r="K88" t="inlineStr">
         <is>
           <t>left</t>
@@ -6516,10 +6516,10 @@
         </is>
       </c>
       <c r="M88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O88" t="n">
         <v>1.2</v>
@@ -6528,10 +6528,10 @@
         <v>0.2</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.26</v>
+        <v>0.42</v>
       </c>
       <c r="R88" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="S88" t="n">
         <v>3</v>
@@ -6564,12 +6564,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
@@ -6578,12 +6578,12 @@
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O89" t="n">
         <v>2</v>
@@ -6624,12 +6624,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
@@ -6645,19 +6645,19 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O90" t="n">
         <v>1.2</v>
@@ -6666,10 +6666,10 @@
         <v>0.2</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.45</v>
+        <v>0.74</v>
       </c>
       <c r="R90" t="n">
-        <v>2.17</v>
+        <v>1.9</v>
       </c>
       <c r="S90" t="n">
         <v>3</v>
@@ -6702,12 +6702,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
@@ -6716,12 +6716,12 @@
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O91" t="n">
         <v>2</v>
@@ -6762,25 +6762,25 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="K92" t="inlineStr">
         <is>
           <t>left</t>
@@ -6792,10 +6792,10 @@
         </is>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N92" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O92" t="n">
         <v>1.2</v>
@@ -6804,10 +6804,10 @@
         <v>0.2</v>
       </c>
       <c r="Q92" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.54</v>
       </c>
       <c r="R92" t="n">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="S92" t="n">
         <v>3</v>
@@ -6840,12 +6840,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
@@ -6854,12 +6854,12 @@
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O93" t="n">
         <v>2</v>
@@ -6900,25 +6900,25 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
       <c r="K94" t="inlineStr">
         <is>
           <t>right</t>
@@ -6930,10 +6930,10 @@
         </is>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N94" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O94" t="n">
         <v>1.2</v>
@@ -6942,10 +6942,10 @@
         <v>0.2</v>
       </c>
       <c r="Q94" t="n">
-        <v>0.6</v>
+        <v>0.73</v>
       </c>
       <c r="R94" t="n">
-        <v>2.22</v>
+        <v>1.77</v>
       </c>
       <c r="S94" t="n">
         <v>3</v>
@@ -6978,12 +6978,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
@@ -6992,12 +6992,12 @@
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M95" t="inlineStr"/>
       <c r="N95" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O95" t="n">
         <v>2</v>
@@ -7038,12 +7038,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
@@ -7059,19 +7059,19 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O96" t="n">
         <v>1.2</v>
@@ -7080,10 +7080,10 @@
         <v>0.2</v>
       </c>
       <c r="Q96" t="n">
-        <v>0.28</v>
+        <v>0.58</v>
       </c>
       <c r="R96" t="n">
-        <v>1.99</v>
+        <v>1.79</v>
       </c>
       <c r="S96" t="n">
         <v>3</v>
@@ -7116,12 +7116,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
@@ -7130,12 +7130,12 @@
       <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M97" t="inlineStr"/>
       <c r="N97" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O97" t="n">
         <v>2</v>
@@ -7176,25 +7176,25 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
       <c r="K98" t="inlineStr">
         <is>
           <t>left</t>
@@ -7206,10 +7206,10 @@
         </is>
       </c>
       <c r="M98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O98" t="n">
         <v>1.2</v>
@@ -7218,10 +7218,10 @@
         <v>0.2</v>
       </c>
       <c r="Q98" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="R98" t="n">
-        <v>1.87</v>
+        <v>2.19</v>
       </c>
       <c r="S98" t="n">
         <v>3</v>
@@ -7254,12 +7254,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="H99" t="inlineStr"/>
@@ -7268,12 +7268,12 @@
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M99" t="inlineStr"/>
       <c r="N99" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O99" t="n">
         <v>2</v>
@@ -7314,12 +7314,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
@@ -7335,19 +7335,19 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N100" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O100" t="n">
         <v>1.2</v>
@@ -7356,10 +7356,10 @@
         <v>0.2</v>
       </c>
       <c r="Q100" t="n">
-        <v>0.68</v>
+        <v>0.72</v>
       </c>
       <c r="R100" t="n">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="S100" t="n">
         <v>3</v>
@@ -7392,12 +7392,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
@@ -7406,12 +7406,12 @@
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M101" t="inlineStr"/>
       <c r="N101" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O101" t="n">
         <v>2</v>
@@ -7452,12 +7452,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
@@ -7473,19 +7473,19 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N102" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O102" t="n">
         <v>1.2</v>
@@ -7494,10 +7494,10 @@
         <v>0.2</v>
       </c>
       <c r="Q102" t="n">
-        <v>0.75</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="R102" t="n">
-        <v>2.21</v>
+        <v>2.16</v>
       </c>
       <c r="S102" t="n">
         <v>3</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="H103" t="inlineStr"/>
@@ -7544,12 +7544,12 @@
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M103" t="inlineStr"/>
       <c r="N103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O103" t="n">
         <v>2</v>
@@ -7590,25 +7590,25 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="K104" t="inlineStr">
         <is>
           <t>right</t>
@@ -7620,7 +7620,7 @@
         </is>
       </c>
       <c r="M104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
         <v>5</v>
@@ -7632,10 +7632,10 @@
         <v>0.2</v>
       </c>
       <c r="Q104" t="n">
-        <v>0.38</v>
+        <v>0.29</v>
       </c>
       <c r="R104" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S104" t="n">
         <v>3</v>
@@ -7668,12 +7668,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
@@ -7733,20 +7733,20 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
       <c r="K106" t="inlineStr">
         <is>
           <t>right</t>
@@ -7758,10 +7758,10 @@
         </is>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N106" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O106" t="n">
         <v>1.2</v>
@@ -7770,10 +7770,10 @@
         <v>0.2</v>
       </c>
       <c r="Q106" t="n">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="R106" t="n">
-        <v>1.8</v>
+        <v>2.12</v>
       </c>
       <c r="S106" t="n">
         <v>3</v>
@@ -7811,7 +7811,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
@@ -7820,12 +7820,12 @@
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M107" t="inlineStr"/>
       <c r="N107" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O107" t="n">
         <v>2</v>
@@ -7866,12 +7866,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
@@ -7887,16 +7887,16 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
         <v>2</v>
@@ -7911,7 +7911,7 @@
         <v>0.33</v>
       </c>
       <c r="R108" t="n">
-        <v>2.04</v>
+        <v>1.77</v>
       </c>
       <c r="S108" t="n">
         <v>3</v>
@@ -7944,12 +7944,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
@@ -8004,12 +8004,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
@@ -8025,19 +8025,19 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O110" t="n">
         <v>1.2</v>
@@ -8046,10 +8046,10 @@
         <v>0.2</v>
       </c>
       <c r="Q110" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="R110" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="S110" t="n">
         <v>3</v>
@@ -8082,12 +8082,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
@@ -8096,12 +8096,12 @@
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M111" t="inlineStr"/>
       <c r="N111" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O111" t="n">
         <v>2</v>
@@ -8142,25 +8142,25 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_14.jpg</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
           <t>stimuli/jacket/jacket_27.jpg</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="K112" t="inlineStr">
         <is>
           <t>left</t>
@@ -8172,7 +8172,7 @@
         </is>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N112" t="n">
         <v>3</v>
@@ -8184,10 +8184,10 @@
         <v>0.2</v>
       </c>
       <c r="Q112" t="n">
-        <v>0.75</v>
+        <v>0.4</v>
       </c>
       <c r="R112" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="S112" t="n">
         <v>3</v>
@@ -8220,12 +8220,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_14.jpg</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
           <t>stimuli/jacket/jacket_27.jpg</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="H113" t="inlineStr"/>
@@ -8285,7 +8285,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
@@ -8301,19 +8301,19 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O114" t="n">
         <v>1.2</v>
@@ -8322,10 +8322,10 @@
         <v>0.2</v>
       </c>
       <c r="Q114" t="n">
-        <v>0.27</v>
+        <v>0.45</v>
       </c>
       <c r="R114" t="n">
-        <v>1.88</v>
+        <v>2.25</v>
       </c>
       <c r="S114" t="n">
         <v>3</v>
@@ -8363,7 +8363,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="H115" t="inlineStr"/>
@@ -8372,12 +8372,12 @@
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M115" t="inlineStr"/>
       <c r="N115" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O115" t="n">
         <v>2</v>
@@ -8423,20 +8423,20 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
       <c r="K116" t="inlineStr">
         <is>
           <t>right</t>
@@ -8448,10 +8448,10 @@
         </is>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N116" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O116" t="n">
         <v>1.2</v>
@@ -8460,10 +8460,10 @@
         <v>0.2</v>
       </c>
       <c r="Q116" t="n">
-        <v>0.65</v>
+        <v>0.73</v>
       </c>
       <c r="R116" t="n">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="S116" t="n">
         <v>3</v>
@@ -8501,7 +8501,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
@@ -8510,12 +8510,12 @@
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M117" t="inlineStr"/>
       <c r="N117" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O117" t="n">
         <v>2</v>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -8589,7 +8589,7 @@
         <v>1</v>
       </c>
       <c r="N118" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O118" t="n">
         <v>1.2</v>
@@ -8598,10 +8598,10 @@
         <v>0.2</v>
       </c>
       <c r="Q118" t="n">
-        <v>0.34</v>
+        <v>0.68</v>
       </c>
       <c r="R118" t="n">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="S118" t="n">
         <v>3</v>
@@ -8634,7 +8634,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -8648,12 +8648,12 @@
       <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M119" t="inlineStr"/>
       <c r="N119" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O119" t="n">
         <v>2</v>
@@ -8694,40 +8694,40 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M120" t="n">
         <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O120" t="n">
         <v>1.2</v>
@@ -8736,10 +8736,10 @@
         <v>0.2</v>
       </c>
       <c r="Q120" t="n">
-        <v>0.64</v>
+        <v>0.43</v>
       </c>
       <c r="R120" t="n">
-        <v>2.11</v>
+        <v>1.96</v>
       </c>
       <c r="S120" t="n">
         <v>3</v>
@@ -8772,12 +8772,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
@@ -8786,12 +8786,12 @@
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M121" t="inlineStr"/>
       <c r="N121" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O121" t="n">
         <v>2</v>
@@ -8832,33 +8832,33 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M122" t="n">
@@ -8874,10 +8874,10 @@
         <v>0.2</v>
       </c>
       <c r="Q122" t="n">
-        <v>0.73</v>
+        <v>0.26</v>
       </c>
       <c r="R122" t="n">
-        <v>1.76</v>
+        <v>2.08</v>
       </c>
       <c r="S122" t="n">
         <v>4</v>
@@ -8910,12 +8910,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
@@ -9012,10 +9012,10 @@
         <v>0.2</v>
       </c>
       <c r="Q124" t="n">
-        <v>0.71</v>
+        <v>0.33</v>
       </c>
       <c r="R124" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="S124" t="n">
         <v>4</v>
@@ -9108,12 +9108,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
@@ -9141,7 +9141,7 @@
         <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O126" t="n">
         <v>1.2</v>
@@ -9150,10 +9150,10 @@
         <v>0.2</v>
       </c>
       <c r="Q126" t="n">
-        <v>0.64</v>
+        <v>0.35</v>
       </c>
       <c r="R126" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="S126" t="n">
         <v>4</v>
@@ -9186,12 +9186,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
@@ -9200,12 +9200,12 @@
       <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M127" t="inlineStr"/>
       <c r="N127" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O127" t="n">
         <v>2</v>
@@ -9246,40 +9246,40 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
+          <t>stimuli/house/house_35.jpg</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_27.jpg</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M128" t="n">
         <v>1</v>
       </c>
       <c r="N128" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O128" t="n">
         <v>1.2</v>
@@ -9288,10 +9288,10 @@
         <v>0.2</v>
       </c>
       <c r="Q128" t="n">
-        <v>0.37</v>
+        <v>0.75</v>
       </c>
       <c r="R128" t="n">
-        <v>1.83</v>
+        <v>2.21</v>
       </c>
       <c r="S128" t="n">
         <v>4</v>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
+          <t>stimuli/house/house_35.jpg</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_27.jpg</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
@@ -9338,12 +9338,12 @@
       <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M129" t="inlineStr"/>
       <c r="N129" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O129" t="n">
         <v>2</v>
@@ -9389,7 +9389,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
@@ -9417,7 +9417,7 @@
         <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O130" t="n">
         <v>1.2</v>
@@ -9426,10 +9426,10 @@
         <v>0.2</v>
       </c>
       <c r="Q130" t="n">
-        <v>0.62</v>
+        <v>0.38</v>
       </c>
       <c r="R130" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="S130" t="n">
         <v>4</v>
@@ -9467,7 +9467,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
@@ -9476,12 +9476,12 @@
       <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M131" t="inlineStr"/>
       <c r="N131" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O131" t="n">
         <v>2</v>
@@ -9522,40 +9522,40 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M132" t="n">
         <v>1</v>
       </c>
       <c r="N132" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O132" t="n">
         <v>1.2</v>
@@ -9564,10 +9564,10 @@
         <v>0.2</v>
       </c>
       <c r="Q132" t="n">
-        <v>0.68</v>
+        <v>0.57</v>
       </c>
       <c r="R132" t="n">
-        <v>2.18</v>
+        <v>2.01</v>
       </c>
       <c r="S132" t="n">
         <v>4</v>
@@ -9600,12 +9600,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
@@ -9614,12 +9614,12 @@
       <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M133" t="inlineStr"/>
       <c r="N133" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O133" t="n">
         <v>2</v>
@@ -9660,25 +9660,25 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
       <c r="K134" t="inlineStr">
         <is>
           <t>right</t>
@@ -9690,7 +9690,7 @@
         </is>
       </c>
       <c r="M134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N134" t="n">
         <v>4</v>
@@ -9702,10 +9702,10 @@
         <v>0.2</v>
       </c>
       <c r="Q134" t="n">
-        <v>0.42</v>
+        <v>0.72</v>
       </c>
       <c r="R134" t="n">
-        <v>1.99</v>
+        <v>2.13</v>
       </c>
       <c r="S134" t="n">
         <v>4</v>
@@ -9738,12 +9738,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
@@ -9798,12 +9798,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="H136" t="inlineStr"/>
@@ -9819,19 +9819,19 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N136" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O136" t="n">
         <v>1.2</v>
@@ -9840,10 +9840,10 @@
         <v>0.2</v>
       </c>
       <c r="Q136" t="n">
-        <v>0.63</v>
+        <v>0.57</v>
       </c>
       <c r="R136" t="n">
-        <v>1.79</v>
+        <v>2.04</v>
       </c>
       <c r="S136" t="n">
         <v>4</v>
@@ -9876,12 +9876,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
@@ -9890,12 +9890,12 @@
       <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M137" t="inlineStr"/>
       <c r="N137" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O137" t="n">
         <v>2</v>
@@ -9936,33 +9936,33 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M138" t="n">
@@ -9978,10 +9978,10 @@
         <v>0.2</v>
       </c>
       <c r="Q138" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="R138" t="n">
-        <v>2.02</v>
+        <v>2.22</v>
       </c>
       <c r="S138" t="n">
         <v>4</v>
@@ -10014,12 +10014,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="H139" t="inlineStr"/>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="H140" t="inlineStr"/>
@@ -10116,10 +10116,10 @@
         <v>0.2</v>
       </c>
       <c r="Q140" t="n">
-        <v>0.65</v>
+        <v>0.55</v>
       </c>
       <c r="R140" t="n">
-        <v>2.17</v>
+        <v>1.88</v>
       </c>
       <c r="S140" t="n">
         <v>4</v>
@@ -10152,12 +10152,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="H141" t="inlineStr"/>
@@ -10212,7 +10212,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -10223,14 +10223,14 @@
       <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
       <c r="K142" t="inlineStr">
         <is>
           <t>right</t>
@@ -10242,7 +10242,7 @@
         </is>
       </c>
       <c r="M142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N142" t="n">
         <v>2</v>
@@ -10254,10 +10254,10 @@
         <v>0.2</v>
       </c>
       <c r="Q142" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="R142" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="S142" t="n">
         <v>4</v>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -10350,12 +10350,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="H144" t="inlineStr"/>
@@ -10371,16 +10371,16 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N144" t="n">
         <v>5</v>
@@ -10392,10 +10392,10 @@
         <v>0.2</v>
       </c>
       <c r="Q144" t="n">
-        <v>0.49</v>
+        <v>0.44</v>
       </c>
       <c r="R144" t="n">
-        <v>2.17</v>
+        <v>1.81</v>
       </c>
       <c r="S144" t="n">
         <v>4</v>
@@ -10428,12 +10428,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="H145" t="inlineStr"/>
@@ -10488,12 +10488,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="H146" t="inlineStr"/>
@@ -10521,7 +10521,7 @@
         <v>0</v>
       </c>
       <c r="N146" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O146" t="n">
         <v>1.2</v>
@@ -10530,10 +10530,10 @@
         <v>0.2</v>
       </c>
       <c r="Q146" t="n">
-        <v>0.45</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R146" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="S146" t="n">
         <v>4</v>
@@ -10566,12 +10566,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="H147" t="inlineStr"/>
@@ -10580,12 +10580,12 @@
       <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M147" t="inlineStr"/>
       <c r="N147" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O147" t="n">
         <v>2</v>
@@ -10626,33 +10626,33 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M148" t="n">
@@ -10668,10 +10668,10 @@
         <v>0.2</v>
       </c>
       <c r="Q148" t="n">
-        <v>0.38</v>
+        <v>0.64</v>
       </c>
       <c r="R148" t="n">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="S148" t="n">
         <v>4</v>
@@ -10704,12 +10704,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="H149" t="inlineStr"/>
@@ -10764,40 +10764,40 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M150" t="n">
         <v>1</v>
       </c>
       <c r="N150" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O150" t="n">
         <v>1.2</v>
@@ -10806,10 +10806,10 @@
         <v>0.2</v>
       </c>
       <c r="Q150" t="n">
-        <v>0.73</v>
+        <v>0.44</v>
       </c>
       <c r="R150" t="n">
-        <v>2.03</v>
+        <v>2.21</v>
       </c>
       <c r="S150" t="n">
         <v>4</v>
@@ -10842,12 +10842,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="H151" t="inlineStr"/>
@@ -10856,12 +10856,12 @@
       <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M151" t="inlineStr"/>
       <c r="N151" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O151" t="n">
         <v>2</v>
@@ -10902,12 +10902,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="H152" t="inlineStr"/>
@@ -10935,7 +10935,7 @@
         <v>0</v>
       </c>
       <c r="N152" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O152" t="n">
         <v>1.2</v>
@@ -10944,10 +10944,10 @@
         <v>0.2</v>
       </c>
       <c r="Q152" t="n">
-        <v>0.72</v>
+        <v>0.67</v>
       </c>
       <c r="R152" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="S152" t="n">
         <v>4</v>
@@ -10980,12 +10980,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="H153" t="inlineStr"/>
@@ -10994,12 +10994,12 @@
       <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M153" t="inlineStr"/>
       <c r="N153" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O153" t="n">
         <v>2</v>
@@ -11040,12 +11040,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="H154" t="inlineStr"/>
@@ -11061,19 +11061,19 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N154" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O154" t="n">
         <v>1.2</v>
@@ -11082,10 +11082,10 @@
         <v>0.2</v>
       </c>
       <c r="Q154" t="n">
-        <v>0.34</v>
+        <v>0.3</v>
       </c>
       <c r="R154" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="S154" t="n">
         <v>4</v>
@@ -11118,12 +11118,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="H155" t="inlineStr"/>
@@ -11132,12 +11132,12 @@
       <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M155" t="inlineStr"/>
       <c r="N155" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O155" t="n">
         <v>2</v>
@@ -11178,25 +11178,25 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
       <c r="K156" t="inlineStr">
         <is>
           <t>left</t>
@@ -11208,10 +11208,10 @@
         </is>
       </c>
       <c r="M156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N156" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O156" t="n">
         <v>1.2</v>
@@ -11220,10 +11220,10 @@
         <v>0.2</v>
       </c>
       <c r="Q156" t="n">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
       <c r="R156" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="S156" t="n">
         <v>4</v>
@@ -11256,12 +11256,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="H157" t="inlineStr"/>
@@ -11270,12 +11270,12 @@
       <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M157" t="inlineStr"/>
       <c r="N157" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O157" t="n">
         <v>2</v>
@@ -11316,25 +11316,25 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="H158" t="inlineStr"/>
       <c r="I158" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="K158" t="inlineStr">
         <is>
           <t>right</t>
@@ -11346,10 +11346,10 @@
         </is>
       </c>
       <c r="M158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N158" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O158" t="n">
         <v>1.2</v>
@@ -11358,10 +11358,10 @@
         <v>0.2</v>
       </c>
       <c r="Q158" t="n">
-        <v>0.57</v>
+        <v>0.66</v>
       </c>
       <c r="R158" t="n">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="S158" t="n">
         <v>4</v>
@@ -11394,12 +11394,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="H159" t="inlineStr"/>
@@ -11408,12 +11408,12 @@
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M159" t="inlineStr"/>
       <c r="N159" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O159" t="n">
         <v>2</v>
@@ -11454,12 +11454,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
+          <t>stimuli/hammer/hammer_19.jpg</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
           <t>stimuli/bicycle/bicycle_12.jpg</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="H160" t="inlineStr"/>
@@ -11475,19 +11475,19 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N160" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O160" t="n">
         <v>1.2</v>
@@ -11496,10 +11496,10 @@
         <v>0.2</v>
       </c>
       <c r="Q160" t="n">
-        <v>0.52</v>
+        <v>0.33</v>
       </c>
       <c r="R160" t="n">
-        <v>2.17</v>
+        <v>2.03</v>
       </c>
       <c r="S160" t="n">
         <v>4</v>
@@ -11532,12 +11532,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
+          <t>stimuli/hammer/hammer_19.jpg</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
           <t>stimuli/bicycle/bicycle_12.jpg</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="H161" t="inlineStr"/>
@@ -11546,12 +11546,12 @@
       <c r="K161" t="inlineStr"/>
       <c r="L161" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M161" t="inlineStr"/>
       <c r="N161" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O161" t="n">
         <v>2</v>
@@ -11592,12 +11592,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="H162" t="inlineStr"/>
@@ -11613,19 +11613,19 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N162" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O162" t="n">
         <v>1.2</v>
@@ -11634,10 +11634,10 @@
         <v>0.2</v>
       </c>
       <c r="Q162" t="n">
-        <v>0.31</v>
+        <v>0.75</v>
       </c>
       <c r="R162" t="n">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="S162" t="n">
         <v>5</v>
@@ -11670,12 +11670,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="H163" t="inlineStr"/>
@@ -11684,12 +11684,12 @@
       <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M163" t="inlineStr"/>
       <c r="N163" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O163" t="n">
         <v>2</v>
@@ -11730,25 +11730,25 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="H164" t="inlineStr"/>
       <c r="I164" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
       <c r="K164" t="inlineStr">
         <is>
           <t>left</t>
@@ -11760,10 +11760,10 @@
         </is>
       </c>
       <c r="M164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N164" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O164" t="n">
         <v>1.2</v>
@@ -11772,10 +11772,10 @@
         <v>0.2</v>
       </c>
       <c r="Q164" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="R164" t="n">
-        <v>2.23</v>
+        <v>1.95</v>
       </c>
       <c r="S164" t="n">
         <v>5</v>
@@ -11808,12 +11808,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="H165" t="inlineStr"/>
@@ -11822,12 +11822,12 @@
       <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M165" t="inlineStr"/>
       <c r="N165" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O165" t="n">
         <v>2</v>
@@ -11868,25 +11868,25 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J166" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="K166" t="inlineStr">
         <is>
           <t>right</t>
@@ -11898,10 +11898,10 @@
         </is>
       </c>
       <c r="M166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N166" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O166" t="n">
         <v>1.2</v>
@@ -11910,10 +11910,10 @@
         <v>0.2</v>
       </c>
       <c r="Q166" t="n">
-        <v>0.52</v>
+        <v>0.73</v>
       </c>
       <c r="R166" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="S166" t="n">
         <v>5</v>
@@ -11946,12 +11946,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="H167" t="inlineStr"/>
@@ -11960,12 +11960,12 @@
       <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M167" t="inlineStr"/>
       <c r="N167" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O167" t="n">
         <v>2</v>
@@ -12006,12 +12006,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="H168" t="inlineStr"/>
@@ -12027,19 +12027,19 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N168" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O168" t="n">
         <v>1.2</v>
@@ -12048,10 +12048,10 @@
         <v>0.2</v>
       </c>
       <c r="Q168" t="n">
-        <v>0.59</v>
+        <v>0.44</v>
       </c>
       <c r="R168" t="n">
-        <v>2.11</v>
+        <v>2.23</v>
       </c>
       <c r="S168" t="n">
         <v>5</v>
@@ -12084,12 +12084,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="H169" t="inlineStr"/>
@@ -12098,12 +12098,12 @@
       <c r="K169" t="inlineStr"/>
       <c r="L169" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M169" t="inlineStr"/>
       <c r="N169" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O169" t="n">
         <v>2</v>
@@ -12144,40 +12144,40 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J170" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M170" t="n">
         <v>1</v>
       </c>
       <c r="N170" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O170" t="n">
         <v>1.2</v>
@@ -12186,10 +12186,10 @@
         <v>0.2</v>
       </c>
       <c r="Q170" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="R170" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="S170" t="n">
         <v>5</v>
@@ -12222,12 +12222,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="H171" t="inlineStr"/>
@@ -12236,12 +12236,12 @@
       <c r="K171" t="inlineStr"/>
       <c r="L171" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M171" t="inlineStr"/>
       <c r="N171" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O171" t="n">
         <v>2</v>
@@ -12282,40 +12282,40 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="J172" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M172" t="n">
         <v>0</v>
       </c>
       <c r="N172" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O172" t="n">
         <v>1.2</v>
@@ -12324,10 +12324,10 @@
         <v>0.2</v>
       </c>
       <c r="Q172" t="n">
-        <v>0.51</v>
+        <v>0.39</v>
       </c>
       <c r="R172" t="n">
-        <v>2.07</v>
+        <v>2.18</v>
       </c>
       <c r="S172" t="n">
         <v>5</v>
@@ -12360,12 +12360,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="H173" t="inlineStr"/>
@@ -12374,12 +12374,12 @@
       <c r="K173" t="inlineStr"/>
       <c r="L173" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M173" t="inlineStr"/>
       <c r="N173" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O173" t="n">
         <v>2</v>
@@ -12420,12 +12420,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="H174" t="inlineStr"/>
@@ -12441,19 +12441,19 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N174" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O174" t="n">
         <v>1.2</v>
@@ -12462,10 +12462,10 @@
         <v>0.2</v>
       </c>
       <c r="Q174" t="n">
-        <v>0.5</v>
+        <v>0.63</v>
       </c>
       <c r="R174" t="n">
-        <v>2.13</v>
+        <v>1.94</v>
       </c>
       <c r="S174" t="n">
         <v>5</v>
@@ -12498,12 +12498,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="H175" t="inlineStr"/>
@@ -12512,12 +12512,12 @@
       <c r="K175" t="inlineStr"/>
       <c r="L175" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M175" t="inlineStr"/>
       <c r="N175" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O175" t="n">
         <v>2</v>
@@ -12558,12 +12558,12 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="H176" t="inlineStr"/>
@@ -12579,19 +12579,19 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N176" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O176" t="n">
         <v>1.2</v>
@@ -12600,10 +12600,10 @@
         <v>0.2</v>
       </c>
       <c r="Q176" t="n">
-        <v>0.67</v>
+        <v>0.55</v>
       </c>
       <c r="R176" t="n">
-        <v>2.11</v>
+        <v>1.8</v>
       </c>
       <c r="S176" t="n">
         <v>5</v>
@@ -12636,12 +12636,12 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="H177" t="inlineStr"/>
@@ -12650,12 +12650,12 @@
       <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M177" t="inlineStr"/>
       <c r="N177" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O177" t="n">
         <v>2</v>
@@ -12701,35 +12701,35 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="H178" t="inlineStr"/>
       <c r="I178" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="J178" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M178" t="n">
         <v>1</v>
       </c>
       <c r="N178" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O178" t="n">
         <v>1.2</v>
@@ -12738,10 +12738,10 @@
         <v>0.2</v>
       </c>
       <c r="Q178" t="n">
-        <v>0.25</v>
+        <v>0.62</v>
       </c>
       <c r="R178" t="n">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="S178" t="n">
         <v>5</v>
@@ -12779,7 +12779,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="H179" t="inlineStr"/>
@@ -12788,12 +12788,12 @@
       <c r="K179" t="inlineStr"/>
       <c r="L179" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M179" t="inlineStr"/>
       <c r="N179" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O179" t="n">
         <v>2</v>
@@ -12839,7 +12839,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="H180" t="inlineStr"/>
@@ -12867,7 +12867,7 @@
         <v>0</v>
       </c>
       <c r="N180" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O180" t="n">
         <v>1.2</v>
@@ -12876,10 +12876,10 @@
         <v>0.2</v>
       </c>
       <c r="Q180" t="n">
-        <v>0.35</v>
+        <v>0.54</v>
       </c>
       <c r="R180" t="n">
-        <v>2.11</v>
+        <v>1.91</v>
       </c>
       <c r="S180" t="n">
         <v>5</v>
@@ -12917,7 +12917,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="H181" t="inlineStr"/>
@@ -12926,12 +12926,12 @@
       <c r="K181" t="inlineStr"/>
       <c r="L181" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M181" t="inlineStr"/>
       <c r="N181" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O181" t="n">
         <v>2</v>
@@ -12972,12 +12972,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="H182" t="inlineStr"/>
@@ -13014,7 +13014,7 @@
         <v>0.2</v>
       </c>
       <c r="Q182" t="n">
-        <v>0.72</v>
+        <v>0.5</v>
       </c>
       <c r="R182" t="n">
         <v>2.04</v>
@@ -13050,12 +13050,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="H183" t="inlineStr"/>
@@ -13110,40 +13110,40 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_06.jpg</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_27.jpg</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="H184" t="inlineStr"/>
       <c r="I184" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J184" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M184" t="n">
         <v>1</v>
       </c>
       <c r="N184" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O184" t="n">
         <v>1.2</v>
@@ -13152,10 +13152,10 @@
         <v>0.2</v>
       </c>
       <c r="Q184" t="n">
-        <v>0.34</v>
+        <v>0.28</v>
       </c>
       <c r="R184" t="n">
-        <v>1.85</v>
+        <v>2.22</v>
       </c>
       <c r="S184" t="n">
         <v>5</v>
@@ -13188,12 +13188,12 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_06.jpg</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_27.jpg</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="H185" t="inlineStr"/>
@@ -13202,12 +13202,12 @@
       <c r="K185" t="inlineStr"/>
       <c r="L185" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M185" t="inlineStr"/>
       <c r="N185" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O185" t="n">
         <v>2</v>
@@ -13248,12 +13248,12 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="H186" t="inlineStr"/>
@@ -13269,19 +13269,19 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N186" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O186" t="n">
         <v>1.2</v>
@@ -13290,10 +13290,10 @@
         <v>0.2</v>
       </c>
       <c r="Q186" t="n">
-        <v>0.44</v>
+        <v>0.62</v>
       </c>
       <c r="R186" t="n">
-        <v>1.89</v>
+        <v>2.06</v>
       </c>
       <c r="S186" t="n">
         <v>5</v>
@@ -13326,12 +13326,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="H187" t="inlineStr"/>
@@ -13340,12 +13340,12 @@
       <c r="K187" t="inlineStr"/>
       <c r="L187" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M187" t="inlineStr"/>
       <c r="N187" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O187" t="n">
         <v>2</v>
@@ -13386,25 +13386,25 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="H188" t="inlineStr"/>
       <c r="I188" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="J188" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
       <c r="K188" t="inlineStr">
         <is>
           <t>left</t>
@@ -13416,10 +13416,10 @@
         </is>
       </c>
       <c r="M188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N188" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O188" t="n">
         <v>1.2</v>
@@ -13428,10 +13428,10 @@
         <v>0.2</v>
       </c>
       <c r="Q188" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="R188" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="S188" t="n">
         <v>5</v>
@@ -13464,12 +13464,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="H189" t="inlineStr"/>
@@ -13478,12 +13478,12 @@
       <c r="K189" t="inlineStr"/>
       <c r="L189" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M189" t="inlineStr"/>
       <c r="N189" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O189" t="n">
         <v>2</v>
@@ -13524,25 +13524,25 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J190" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="K190" t="inlineStr">
         <is>
           <t>right</t>
@@ -13554,10 +13554,10 @@
         </is>
       </c>
       <c r="M190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N190" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O190" t="n">
         <v>1.2</v>
@@ -13566,10 +13566,10 @@
         <v>0.2</v>
       </c>
       <c r="Q190" t="n">
-        <v>0.54</v>
+        <v>0.51</v>
       </c>
       <c r="R190" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="S190" t="n">
         <v>5</v>
@@ -13602,12 +13602,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="H191" t="inlineStr"/>
@@ -13616,12 +13616,12 @@
       <c r="K191" t="inlineStr"/>
       <c r="L191" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M191" t="inlineStr"/>
       <c r="N191" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O191" t="n">
         <v>2</v>
@@ -13662,7 +13662,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -13683,19 +13683,19 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M192" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N192" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O192" t="n">
         <v>1.2</v>
@@ -13704,10 +13704,10 @@
         <v>0.2</v>
       </c>
       <c r="Q192" t="n">
-        <v>0.42</v>
+        <v>0.6</v>
       </c>
       <c r="R192" t="n">
-        <v>1.93</v>
+        <v>2.16</v>
       </c>
       <c r="S192" t="n">
         <v>5</v>
@@ -13740,7 +13740,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -13754,12 +13754,12 @@
       <c r="K193" t="inlineStr"/>
       <c r="L193" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M193" t="inlineStr"/>
       <c r="N193" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O193" t="n">
         <v>2</v>
@@ -13800,40 +13800,40 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J194" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M194" t="n">
         <v>0</v>
       </c>
       <c r="N194" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O194" t="n">
         <v>1.2</v>
@@ -13842,10 +13842,10 @@
         <v>0.2</v>
       </c>
       <c r="Q194" t="n">
-        <v>0.7</v>
+        <v>0.74</v>
       </c>
       <c r="R194" t="n">
-        <v>2.17</v>
+        <v>1.97</v>
       </c>
       <c r="S194" t="n">
         <v>5</v>
@@ -13878,12 +13878,12 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="H195" t="inlineStr"/>
@@ -13892,12 +13892,12 @@
       <c r="K195" t="inlineStr"/>
       <c r="L195" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M195" t="inlineStr"/>
       <c r="N195" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O195" t="n">
         <v>2</v>
@@ -13938,12 +13938,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="H196" t="inlineStr"/>
@@ -13971,7 +13971,7 @@
         <v>1</v>
       </c>
       <c r="N196" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O196" t="n">
         <v>1.2</v>
@@ -13980,10 +13980,10 @@
         <v>0.2</v>
       </c>
       <c r="Q196" t="n">
-        <v>0.43</v>
+        <v>0.57</v>
       </c>
       <c r="R196" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="S196" t="n">
         <v>5</v>
@@ -14016,12 +14016,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="H197" t="inlineStr"/>
@@ -14030,12 +14030,12 @@
       <c r="K197" t="inlineStr"/>
       <c r="L197" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M197" t="inlineStr"/>
       <c r="N197" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O197" t="n">
         <v>2</v>
@@ -14076,25 +14076,25 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="J198" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
       <c r="K198" t="inlineStr">
         <is>
           <t>left</t>
@@ -14106,10 +14106,10 @@
         </is>
       </c>
       <c r="M198" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N198" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O198" t="n">
         <v>1.2</v>
@@ -14118,10 +14118,10 @@
         <v>0.2</v>
       </c>
       <c r="Q198" t="n">
-        <v>0.41</v>
+        <v>0.67</v>
       </c>
       <c r="R198" t="n">
-        <v>1.78</v>
+        <v>2.11</v>
       </c>
       <c r="S198" t="n">
         <v>5</v>
@@ -14154,12 +14154,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="H199" t="inlineStr"/>
@@ -14168,12 +14168,12 @@
       <c r="K199" t="inlineStr"/>
       <c r="L199" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M199" t="inlineStr"/>
       <c r="N199" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O199" t="n">
         <v>2</v>
@@ -14214,12 +14214,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="H200" t="inlineStr"/>
@@ -14235,19 +14235,19 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M200" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N200" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O200" t="n">
         <v>1.2</v>
@@ -14256,10 +14256,10 @@
         <v>0.2</v>
       </c>
       <c r="Q200" t="n">
-        <v>0.65</v>
+        <v>0.52</v>
       </c>
       <c r="R200" t="n">
-        <v>2.16</v>
+        <v>1.95</v>
       </c>
       <c r="S200" t="n">
         <v>5</v>
@@ -14292,12 +14292,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="H201" t="inlineStr"/>
@@ -14306,12 +14306,12 @@
       <c r="K201" t="inlineStr"/>
       <c r="L201" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M201" t="inlineStr"/>
       <c r="N201" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O201" t="n">
         <v>2</v>
@@ -14352,40 +14352,40 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="H202" t="inlineStr"/>
       <c r="I202" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J202" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M202" t="n">
         <v>1</v>
       </c>
       <c r="N202" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O202" t="n">
         <v>1.2</v>
@@ -14394,10 +14394,10 @@
         <v>0.2</v>
       </c>
       <c r="Q202" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.28</v>
       </c>
       <c r="R202" t="n">
-        <v>2.22</v>
+        <v>1.76</v>
       </c>
       <c r="S202" t="n">
         <v>6</v>
@@ -14430,12 +14430,12 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="H203" t="inlineStr"/>
@@ -14444,12 +14444,12 @@
       <c r="K203" t="inlineStr"/>
       <c r="L203" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M203" t="inlineStr"/>
       <c r="N203" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O203" t="n">
         <v>2</v>
@@ -14495,35 +14495,35 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="H204" t="inlineStr"/>
       <c r="I204" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J204" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M204" t="n">
         <v>0</v>
       </c>
       <c r="N204" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O204" t="n">
         <v>1.2</v>
@@ -14532,10 +14532,10 @@
         <v>0.2</v>
       </c>
       <c r="Q204" t="n">
-        <v>0.41</v>
+        <v>0.52</v>
       </c>
       <c r="R204" t="n">
-        <v>2.04</v>
+        <v>1.76</v>
       </c>
       <c r="S204" t="n">
         <v>6</v>
@@ -14573,7 +14573,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="H205" t="inlineStr"/>
@@ -14582,12 +14582,12 @@
       <c r="K205" t="inlineStr"/>
       <c r="L205" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M205" t="inlineStr"/>
       <c r="N205" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O205" t="n">
         <v>2</v>
@@ -14628,25 +14628,25 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="H206" t="inlineStr"/>
       <c r="I206" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="J206" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
       <c r="K206" t="inlineStr">
         <is>
           <t>right</t>
@@ -14658,10 +14658,10 @@
         </is>
       </c>
       <c r="M206" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N206" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O206" t="n">
         <v>1.2</v>
@@ -14670,10 +14670,10 @@
         <v>0.2</v>
       </c>
       <c r="Q206" t="n">
-        <v>0.42</v>
+        <v>0.51</v>
       </c>
       <c r="R206" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="S206" t="n">
         <v>6</v>
@@ -14706,12 +14706,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="H207" t="inlineStr"/>
@@ -14720,12 +14720,12 @@
       <c r="K207" t="inlineStr"/>
       <c r="L207" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M207" t="inlineStr"/>
       <c r="N207" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O207" t="n">
         <v>2</v>
@@ -14766,25 +14766,25 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="H208" t="inlineStr"/>
       <c r="I208" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="J208" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
       <c r="K208" t="inlineStr">
         <is>
           <t>left</t>
@@ -14796,10 +14796,10 @@
         </is>
       </c>
       <c r="M208" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N208" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O208" t="n">
         <v>1.2</v>
@@ -14808,10 +14808,10 @@
         <v>0.2</v>
       </c>
       <c r="Q208" t="n">
-        <v>0.53</v>
+        <v>0.61</v>
       </c>
       <c r="R208" t="n">
-        <v>2.14</v>
+        <v>1.9</v>
       </c>
       <c r="S208" t="n">
         <v>6</v>
@@ -14844,12 +14844,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="H209" t="inlineStr"/>
@@ -14858,12 +14858,12 @@
       <c r="K209" t="inlineStr"/>
       <c r="L209" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M209" t="inlineStr"/>
       <c r="N209" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O209" t="n">
         <v>2</v>
@@ -14904,25 +14904,25 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="H210" t="inlineStr"/>
       <c r="I210" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="J210" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
       <c r="K210" t="inlineStr">
         <is>
           <t>left</t>
@@ -14934,10 +14934,10 @@
         </is>
       </c>
       <c r="M210" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N210" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O210" t="n">
         <v>1.2</v>
@@ -14946,10 +14946,10 @@
         <v>0.2</v>
       </c>
       <c r="Q210" t="n">
-        <v>0.58</v>
+        <v>0.74</v>
       </c>
       <c r="R210" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="S210" t="n">
         <v>6</v>
@@ -14982,12 +14982,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="H211" t="inlineStr"/>
@@ -14996,12 +14996,12 @@
       <c r="K211" t="inlineStr"/>
       <c r="L211" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M211" t="inlineStr"/>
       <c r="N211" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O211" t="n">
         <v>2</v>
@@ -15042,25 +15042,25 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="H212" t="inlineStr"/>
       <c r="I212" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="J212" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
       <c r="K212" t="inlineStr">
         <is>
           <t>right</t>
@@ -15072,10 +15072,10 @@
         </is>
       </c>
       <c r="M212" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N212" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O212" t="n">
         <v>1.2</v>
@@ -15084,10 +15084,10 @@
         <v>0.2</v>
       </c>
       <c r="Q212" t="n">
-        <v>0.4</v>
+        <v>0.63</v>
       </c>
       <c r="R212" t="n">
-        <v>2.12</v>
+        <v>1.81</v>
       </c>
       <c r="S212" t="n">
         <v>6</v>
@@ -15120,12 +15120,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/jacket/jacket_27.jpg</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="H213" t="inlineStr"/>
@@ -15134,12 +15134,12 @@
       <c r="K213" t="inlineStr"/>
       <c r="L213" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M213" t="inlineStr"/>
       <c r="N213" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O213" t="n">
         <v>2</v>
@@ -15180,40 +15180,40 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="H214" t="inlineStr"/>
       <c r="I214" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J214" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M214" t="n">
         <v>1</v>
       </c>
       <c r="N214" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O214" t="n">
         <v>1.2</v>
@@ -15222,10 +15222,10 @@
         <v>0.2</v>
       </c>
       <c r="Q214" t="n">
-        <v>0.68</v>
+        <v>0.51</v>
       </c>
       <c r="R214" t="n">
-        <v>2.19</v>
+        <v>1.95</v>
       </c>
       <c r="S214" t="n">
         <v>6</v>
@@ -15258,12 +15258,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="H215" t="inlineStr"/>
@@ -15272,12 +15272,12 @@
       <c r="K215" t="inlineStr"/>
       <c r="L215" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M215" t="inlineStr"/>
       <c r="N215" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O215" t="n">
         <v>2</v>
@@ -15323,35 +15323,35 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="H216" t="inlineStr"/>
       <c r="I216" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J216" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M216" t="n">
         <v>0</v>
       </c>
       <c r="N216" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O216" t="n">
         <v>1.2</v>
@@ -15360,10 +15360,10 @@
         <v>0.2</v>
       </c>
       <c r="Q216" t="n">
-        <v>0.49</v>
+        <v>0.55</v>
       </c>
       <c r="R216" t="n">
-        <v>2.06</v>
+        <v>1.84</v>
       </c>
       <c r="S216" t="n">
         <v>6</v>
@@ -15401,7 +15401,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="H217" t="inlineStr"/>
@@ -15410,12 +15410,12 @@
       <c r="K217" t="inlineStr"/>
       <c r="L217" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M217" t="inlineStr"/>
       <c r="N217" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O217" t="n">
         <v>2</v>
@@ -15456,7 +15456,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -15467,14 +15467,14 @@
       <c r="H218" t="inlineStr"/>
       <c r="I218" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="J218" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
       <c r="K218" t="inlineStr">
         <is>
           <t>left</t>
@@ -15486,10 +15486,10 @@
         </is>
       </c>
       <c r="M218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N218" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O218" t="n">
         <v>1.2</v>
@@ -15498,10 +15498,10 @@
         <v>0.2</v>
       </c>
       <c r="Q218" t="n">
-        <v>0.64</v>
+        <v>0.41</v>
       </c>
       <c r="R218" t="n">
-        <v>2.02</v>
+        <v>1.84</v>
       </c>
       <c r="S218" t="n">
         <v>6</v>
@@ -15534,7 +15534,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -15548,12 +15548,12 @@
       <c r="K219" t="inlineStr"/>
       <c r="L219" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M219" t="inlineStr"/>
       <c r="N219" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O219" t="n">
         <v>2</v>
@@ -15594,25 +15594,25 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="H220" t="inlineStr"/>
       <c r="I220" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J220" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="K220" t="inlineStr">
         <is>
           <t>left</t>
@@ -15624,10 +15624,10 @@
         </is>
       </c>
       <c r="M220" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N220" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O220" t="n">
         <v>1.2</v>
@@ -15636,10 +15636,10 @@
         <v>0.2</v>
       </c>
       <c r="Q220" t="n">
-        <v>0.51</v>
+        <v>0.29</v>
       </c>
       <c r="R220" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="S220" t="n">
         <v>6</v>
@@ -15672,12 +15672,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="H221" t="inlineStr"/>
@@ -15686,12 +15686,12 @@
       <c r="K221" t="inlineStr"/>
       <c r="L221" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M221" t="inlineStr"/>
       <c r="N221" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O221" t="n">
         <v>2</v>
@@ -15732,25 +15732,25 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="H222" t="inlineStr"/>
       <c r="I222" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="J222" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
       <c r="K222" t="inlineStr">
         <is>
           <t>right</t>
@@ -15762,10 +15762,10 @@
         </is>
       </c>
       <c r="M222" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N222" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O222" t="n">
         <v>1.2</v>
@@ -15774,10 +15774,10 @@
         <v>0.2</v>
       </c>
       <c r="Q222" t="n">
-        <v>0.28</v>
+        <v>0.57</v>
       </c>
       <c r="R222" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="S222" t="n">
         <v>6</v>
@@ -15810,12 +15810,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/dog/dog_08.jpg</t>
         </is>
       </c>
       <c r="H223" t="inlineStr"/>
@@ -15824,12 +15824,12 @@
       <c r="K223" t="inlineStr"/>
       <c r="L223" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M223" t="inlineStr"/>
       <c r="N223" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O223" t="n">
         <v>2</v>
@@ -15870,25 +15870,25 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="H224" t="inlineStr"/>
       <c r="I224" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J224" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="K224" t="inlineStr">
         <is>
           <t>right</t>
@@ -15900,7 +15900,7 @@
         </is>
       </c>
       <c r="M224" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N224" t="n">
         <v>2</v>
@@ -15912,10 +15912,10 @@
         <v>0.2</v>
       </c>
       <c r="Q224" t="n">
-        <v>0.63</v>
+        <v>0.37</v>
       </c>
       <c r="R224" t="n">
-        <v>1.94</v>
+        <v>2.23</v>
       </c>
       <c r="S224" t="n">
         <v>6</v>
@@ -15948,12 +15948,12 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/bread/bread_06.jpg</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="H225" t="inlineStr"/>
@@ -16008,12 +16008,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
+          <t>stimuli/hand/hand_10.jpg</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_27.jpg</t>
-        </is>
-      </c>
-      <c r="G226" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="H226" t="inlineStr"/>
@@ -16041,7 +16041,7 @@
         <v>1</v>
       </c>
       <c r="N226" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O226" t="n">
         <v>1.2</v>
@@ -16053,7 +16053,7 @@
         <v>0.43</v>
       </c>
       <c r="R226" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="S226" t="n">
         <v>6</v>
@@ -16086,12 +16086,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
+          <t>stimuli/hand/hand_10.jpg</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_27.jpg</t>
-        </is>
-      </c>
-      <c r="G227" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="H227" t="inlineStr"/>
@@ -16100,12 +16100,12 @@
       <c r="K227" t="inlineStr"/>
       <c r="L227" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M227" t="inlineStr"/>
       <c r="N227" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O227" t="n">
         <v>2</v>
@@ -16146,12 +16146,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="H228" t="inlineStr"/>
@@ -16179,7 +16179,7 @@
         <v>0</v>
       </c>
       <c r="N228" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O228" t="n">
         <v>1.2</v>
@@ -16188,7 +16188,7 @@
         <v>0.2</v>
       </c>
       <c r="Q228" t="n">
-        <v>0.57</v>
+        <v>0.61</v>
       </c>
       <c r="R228" t="n">
         <v>1.77</v>
@@ -16224,12 +16224,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/chair/chair_14.jpg</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="H229" t="inlineStr"/>
@@ -16238,12 +16238,12 @@
       <c r="K229" t="inlineStr"/>
       <c r="L229" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M229" t="inlineStr"/>
       <c r="N229" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O229" t="n">
         <v>2</v>
@@ -16284,12 +16284,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
+          <t>stimuli/jacket/jacket_27.jpg</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_06.jpg</t>
-        </is>
-      </c>
-      <c r="G230" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="H230" t="inlineStr"/>
@@ -16317,7 +16317,7 @@
         <v>0</v>
       </c>
       <c r="N230" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O230" t="n">
         <v>1.2</v>
@@ -16326,10 +16326,10 @@
         <v>0.2</v>
       </c>
       <c r="Q230" t="n">
-        <v>0.61</v>
+        <v>0.67</v>
       </c>
       <c r="R230" t="n">
-        <v>2.24</v>
+        <v>1.91</v>
       </c>
       <c r="S230" t="n">
         <v>6</v>
@@ -16362,12 +16362,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
+          <t>stimuli/jacket/jacket_27.jpg</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_06.jpg</t>
-        </is>
-      </c>
-      <c r="G231" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="H231" t="inlineStr"/>
@@ -16376,12 +16376,12 @@
       <c r="K231" t="inlineStr"/>
       <c r="L231" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M231" t="inlineStr"/>
       <c r="N231" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O231" t="n">
         <v>2</v>
@@ -16422,12 +16422,12 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="H232" t="inlineStr"/>
@@ -16464,10 +16464,10 @@
         <v>0.2</v>
       </c>
       <c r="Q232" t="n">
-        <v>0.28</v>
+        <v>0.62</v>
       </c>
       <c r="R232" t="n">
-        <v>2.18</v>
+        <v>1.75</v>
       </c>
       <c r="S232" t="n">
         <v>6</v>
@@ -16500,12 +16500,12 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/hammer/hammer_19.jpg</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/bicycle/bicycle_12.jpg</t>
         </is>
       </c>
       <c r="H233" t="inlineStr"/>
@@ -16560,12 +16560,12 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="H234" t="inlineStr"/>
@@ -16581,19 +16581,19 @@
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M234" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N234" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O234" t="n">
         <v>1.2</v>
@@ -16602,10 +16602,10 @@
         <v>0.2</v>
       </c>
       <c r="Q234" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="R234" t="n">
-        <v>2.19</v>
+        <v>2.02</v>
       </c>
       <c r="S234" t="n">
         <v>6</v>
@@ -16638,12 +16638,12 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/ball/ball_10.jpg</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/flower/flower_27.jpg</t>
         </is>
       </c>
       <c r="H235" t="inlineStr"/>
@@ -16652,12 +16652,12 @@
       <c r="K235" t="inlineStr"/>
       <c r="L235" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M235" t="inlineStr"/>
       <c r="N235" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O235" t="n">
         <v>2</v>
@@ -16698,25 +16698,25 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="H236" t="inlineStr"/>
       <c r="I236" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J236" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="K236" t="inlineStr">
         <is>
           <t>right</t>
@@ -16728,10 +16728,10 @@
         </is>
       </c>
       <c r="M236" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N236" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O236" t="n">
         <v>1.2</v>
@@ -16740,10 +16740,10 @@
         <v>0.2</v>
       </c>
       <c r="Q236" t="n">
-        <v>0.65</v>
+        <v>0.27</v>
       </c>
       <c r="R236" t="n">
-        <v>2.08</v>
+        <v>1.87</v>
       </c>
       <c r="S236" t="n">
         <v>6</v>
@@ -16776,12 +16776,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/hand/hand_10.jpg</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/house/house_35.jpg</t>
         </is>
       </c>
       <c r="H237" t="inlineStr"/>
@@ -16790,12 +16790,12 @@
       <c r="K237" t="inlineStr"/>
       <c r="L237" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M237" t="inlineStr"/>
       <c r="N237" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O237" t="n">
         <v>2</v>
@@ -16878,10 +16878,10 @@
         <v>0.2</v>
       </c>
       <c r="Q238" t="n">
-        <v>0.68</v>
+        <v>0.46</v>
       </c>
       <c r="R238" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="S238" t="n">
         <v>6</v>
@@ -16985,22 +16985,22 @@
       <c r="H240" t="inlineStr"/>
       <c r="I240" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="J240" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M240" t="n">
@@ -17019,7 +17019,7 @@
         <v>0.29</v>
       </c>
       <c r="R240" t="n">
-        <v>1.98</v>
+        <v>2.17</v>
       </c>
       <c r="S240" t="n">
         <v>6</v>

--- a/psychopy_exp_files/sequences/retrieval_block1_fixed-middle-10_48.xlsx
+++ b/psychopy_exp_files/sequences/retrieval_block1_fixed-middle-10_48.xlsx
@@ -567,12 +567,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/jacket/jacket_33.jpg</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -654,12 +654,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/jacket/jacket_33.jpg</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -723,12 +723,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/chair/chair_39.jpg</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -810,12 +810,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/chair/chair_39.jpg</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -879,12 +879,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/hammer/hammer_34.jpg</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/hand/hand_11.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -966,12 +966,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/hammer/hammer_34.jpg</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/hand/hand_11.jpg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -1035,12 +1035,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bicycle/bicycle_36.jpg</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bicycle/bicycle_36.jpg</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -1191,12 +1191,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/hammer/hammer_34.jpg</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -1434,12 +1434,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/hammer/hammer_34.jpg</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -1503,12 +1503,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/hand/hand_11.jpg</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/hand/hand_11.jpg</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -1659,12 +1659,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bicycle/bicycle_36.jpg</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/chair/chair_39.jpg</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -1746,12 +1746,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bicycle/bicycle_36.jpg</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/chair/chair_39.jpg</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -1815,12 +1815,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/hammer/hammer_34.jpg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -1902,12 +1902,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/hammer/hammer_34.jpg</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
@@ -1971,12 +1971,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/jacket/jacket_33.jpg</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -2058,12 +2058,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/jacket/jacket_33.jpg</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
@@ -2127,12 +2127,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bicycle/bicycle_36.jpg</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bicycle/bicycle_36.jpg</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/hand/hand_11.jpg</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/chair/chair_39.jpg</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -2370,12 +2370,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/hand/hand_11.jpg</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/chair/chair_39.jpg</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
@@ -2526,12 +2526,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
@@ -2595,12 +2595,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/hammer/hammer_34.jpg</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
@@ -2682,12 +2682,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/hammer/hammer_34.jpg</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
@@ -2751,12 +2751,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
@@ -2838,12 +2838,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
@@ -2907,12 +2907,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bicycle/bicycle_36.jpg</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/jacket/jacket_33.jpg</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
@@ -2994,12 +2994,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bicycle/bicycle_36.jpg</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/jacket/jacket_33.jpg</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
@@ -3063,12 +3063,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
@@ -3150,12 +3150,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
@@ -3219,12 +3219,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bicycle/bicycle_36.jpg</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
@@ -3306,12 +3306,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bicycle/bicycle_36.jpg</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
@@ -3375,12 +3375,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -3462,12 +3462,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
@@ -3531,12 +3531,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/hand/hand_11.jpg</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/jacket/jacket_33.jpg</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
@@ -3618,12 +3618,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/hand/hand_11.jpg</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/jacket/jacket_33.jpg</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
@@ -3774,12 +3774,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
@@ -3843,12 +3843,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/hammer/hammer_34.jpg</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
@@ -3930,12 +3930,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/hammer/hammer_34.jpg</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
@@ -3999,12 +3999,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/hand/hand_11.jpg</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
@@ -4086,12 +4086,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/hand/hand_11.jpg</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
@@ -4155,12 +4155,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bicycle/bicycle_36.jpg</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/chair/chair_39.jpg</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
@@ -4242,12 +4242,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bicycle/bicycle_36.jpg</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/chair/chair_39.jpg</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
@@ -4311,12 +4311,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
@@ -4467,12 +4467,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/chair/chair_39.jpg</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
@@ -4554,12 +4554,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/chair/chair_39.jpg</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
@@ -4623,12 +4623,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/hammer/hammer_34.jpg</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/hand/hand_11.jpg</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
@@ -4710,12 +4710,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/hammer/hammer_34.jpg</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/hand/hand_11.jpg</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
@@ -4779,12 +4779,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bicycle/bicycle_36.jpg</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
@@ -4866,12 +4866,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bicycle/bicycle_36.jpg</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/chair/chair_39.jpg</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
@@ -5022,12 +5022,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/chair/chair_39.jpg</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
@@ -5091,12 +5091,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
@@ -5178,12 +5178,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
@@ -5247,12 +5247,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/jacket/jacket_33.jpg</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
@@ -5334,12 +5334,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/jacket/jacket_33.jpg</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
@@ -5403,12 +5403,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/hammer/hammer_34.jpg</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bicycle/bicycle_36.jpg</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
@@ -5490,12 +5490,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/hammer/hammer_34.jpg</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bicycle/bicycle_36.jpg</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
@@ -5559,12 +5559,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/hand/hand_11.jpg</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
@@ -5646,12 +5646,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/hand/hand_11.jpg</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
@@ -5715,12 +5715,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bicycle/bicycle_36.jpg</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/jacket/jacket_33.jpg</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
@@ -5802,12 +5802,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bicycle/bicycle_36.jpg</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/jacket/jacket_33.jpg</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
@@ -5871,12 +5871,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
@@ -5958,12 +5958,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
@@ -6027,12 +6027,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/hammer/hammer_34.jpg</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/hammer/hammer_34.jpg</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
@@ -6183,12 +6183,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/jacket/jacket_33.jpg</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
@@ -6270,12 +6270,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/jacket/jacket_33.jpg</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
@@ -6339,12 +6339,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/chair/chair_39.jpg</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/hand/hand_11.jpg</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
@@ -6426,12 +6426,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/chair/chair_39.jpg</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/hand/hand_11.jpg</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
@@ -6495,12 +6495,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
@@ -6582,12 +6582,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
@@ -6651,12 +6651,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bicycle/bicycle_36.jpg</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
@@ -6738,12 +6738,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bicycle/bicycle_36.jpg</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
@@ -6807,12 +6807,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/hand/hand_11.jpg</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/chair/chair_39.jpg</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/hand/hand_11.jpg</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/chair/chair_39.jpg</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
@@ -6963,12 +6963,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/jacket/jacket_33.jpg</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
@@ -7050,12 +7050,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/jacket/jacket_33.jpg</t>
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
@@ -7119,12 +7119,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bicycle/bicycle_36.jpg</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
@@ -7206,12 +7206,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bicycle/bicycle_36.jpg</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
@@ -7275,12 +7275,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/hammer/hammer_34.jpg</t>
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
@@ -7362,12 +7362,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/hammer/hammer_34.jpg</t>
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
@@ -7431,12 +7431,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bicycle/bicycle_36.jpg</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
@@ -7518,12 +7518,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bicycle/bicycle_36.jpg</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
@@ -7587,12 +7587,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/chair/chair_39.jpg</t>
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
@@ -7674,12 +7674,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/chair/chair_39.jpg</t>
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
@@ -7743,12 +7743,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/jacket/jacket_33.jpg</t>
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
@@ -7830,12 +7830,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/jacket/jacket_33.jpg</t>
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/hand/hand_11.jpg</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/hammer/hammer_34.jpg</t>
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
@@ -7986,12 +7986,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/hand/hand_11.jpg</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/hammer/hammer_34.jpg</t>
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
@@ -8055,12 +8055,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bicycle/bicycle_36.jpg</t>
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
@@ -8142,12 +8142,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bicycle/bicycle_36.jpg</t>
         </is>
       </c>
       <c r="H99" t="inlineStr"/>
@@ -8211,12 +8211,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/hand/hand_11.jpg</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/jacket/jacket_33.jpg</t>
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
@@ -8298,12 +8298,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/hand/hand_11.jpg</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/jacket/jacket_33.jpg</t>
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
@@ -8367,12 +8367,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
@@ -8454,12 +8454,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="H103" t="inlineStr"/>
@@ -8523,12 +8523,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="H104" t="inlineStr"/>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
@@ -8679,12 +8679,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/chair/chair_39.jpg</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bicycle/bicycle_36.jpg</t>
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
@@ -8766,12 +8766,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/chair/chair_39.jpg</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bicycle/bicycle_36.jpg</t>
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
@@ -8835,12 +8835,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/hammer/hammer_34.jpg</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/hammer/hammer_34.jpg</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
@@ -8991,12 +8991,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
@@ -9078,12 +9078,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
@@ -9147,12 +9147,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/hand/hand_11.jpg</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/hand/hand_11.jpg</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="H113" t="inlineStr"/>
@@ -9303,12 +9303,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bicycle/bicycle_36.jpg</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/jacket/jacket_33.jpg</t>
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
@@ -9390,12 +9390,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bicycle/bicycle_36.jpg</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/jacket/jacket_33.jpg</t>
         </is>
       </c>
       <c r="H115" t="inlineStr"/>
@@ -9459,12 +9459,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
@@ -9546,12 +9546,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
@@ -9615,12 +9615,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/hammer/hammer_34.jpg</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
@@ -9702,12 +9702,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/hammer/hammer_34.jpg</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
@@ -9771,12 +9771,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
@@ -9858,12 +9858,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
@@ -9927,12 +9927,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bicycle/bicycle_36.jpg</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/hammer/hammer_34.jpg</t>
         </is>
       </c>
       <c r="H122" t="inlineStr"/>
@@ -10014,12 +10014,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bicycle/bicycle_36.jpg</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/hammer/hammer_34.jpg</t>
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
@@ -10083,12 +10083,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/chair/chair_39.jpg</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
@@ -10170,12 +10170,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/chair/chair_39.jpg</t>
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
@@ -10239,12 +10239,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/jacket/jacket_33.jpg</t>
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
@@ -10326,12 +10326,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/jacket/jacket_33.jpg</t>
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
@@ -10395,12 +10395,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="H128" t="inlineStr"/>
@@ -10482,12 +10482,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
@@ -10551,12 +10551,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bicycle/bicycle_36.jpg</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
@@ -10638,12 +10638,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bicycle/bicycle_36.jpg</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
@@ -10707,12 +10707,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/hammer/hammer_34.jpg</t>
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
@@ -10794,12 +10794,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/hammer/hammer_34.jpg</t>
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
@@ -10863,12 +10863,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/hand/hand_11.jpg</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/chair/chair_39.jpg</t>
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
@@ -10950,12 +10950,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/hand/hand_11.jpg</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/chair/chair_39.jpg</t>
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
@@ -11019,12 +11019,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/jacket/jacket_33.jpg</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="H136" t="inlineStr"/>
@@ -11106,12 +11106,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/jacket/jacket_33.jpg</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
@@ -11175,12 +11175,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/chair/chair_39.jpg</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="H138" t="inlineStr"/>
@@ -11262,12 +11262,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/chair/chair_39.jpg</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="H139" t="inlineStr"/>
@@ -11331,12 +11331,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/hammer/hammer_34.jpg</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/hand/hand_11.jpg</t>
         </is>
       </c>
       <c r="H140" t="inlineStr"/>
@@ -11418,12 +11418,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/hammer/hammer_34.jpg</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/hand/hand_11.jpg</t>
         </is>
       </c>
       <c r="H141" t="inlineStr"/>
@@ -11487,12 +11487,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="H142" t="inlineStr"/>
@@ -11574,12 +11574,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="H143" t="inlineStr"/>
@@ -11643,12 +11643,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bicycle/bicycle_36.jpg</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="H144" t="inlineStr"/>
@@ -11730,12 +11730,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bicycle/bicycle_36.jpg</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="H145" t="inlineStr"/>
@@ -11799,12 +11799,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="H146" t="inlineStr"/>
@@ -11886,12 +11886,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="H147" t="inlineStr"/>
@@ -11955,12 +11955,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/hammer/hammer_34.jpg</t>
         </is>
       </c>
       <c r="H148" t="inlineStr"/>
@@ -12042,12 +12042,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/hammer/hammer_34.jpg</t>
         </is>
       </c>
       <c r="H149" t="inlineStr"/>
@@ -12111,12 +12111,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/hand/hand_11.jpg</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/jacket/jacket_33.jpg</t>
         </is>
       </c>
       <c r="H150" t="inlineStr"/>
@@ -12198,12 +12198,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/hand/hand_11.jpg</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/jacket/jacket_33.jpg</t>
         </is>
       </c>
       <c r="H151" t="inlineStr"/>
@@ -12267,12 +12267,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/chair/chair_39.jpg</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="H152" t="inlineStr"/>
@@ -12354,12 +12354,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/chair/chair_39.jpg</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="H153" t="inlineStr"/>
@@ -12423,12 +12423,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/hammer/hammer_34.jpg</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="H154" t="inlineStr"/>
@@ -12510,12 +12510,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/hammer/hammer_34.jpg</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="H155" t="inlineStr"/>
@@ -12579,12 +12579,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/jacket/jacket_33.jpg</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bicycle/bicycle_36.jpg</t>
         </is>
       </c>
       <c r="H156" t="inlineStr"/>
@@ -12666,12 +12666,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/jacket/jacket_33.jpg</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bicycle/bicycle_36.jpg</t>
         </is>
       </c>
       <c r="H157" t="inlineStr"/>
@@ -12735,12 +12735,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="H158" t="inlineStr"/>
@@ -12822,12 +12822,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="H159" t="inlineStr"/>
@@ -12891,12 +12891,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="H160" t="inlineStr"/>
@@ -12978,12 +12978,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="H161" t="inlineStr"/>
@@ -13047,12 +13047,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bicycle/bicycle_36.jpg</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/hammer/hammer_34.jpg</t>
         </is>
       </c>
       <c r="H162" t="inlineStr"/>
@@ -13134,12 +13134,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bicycle/bicycle_36.jpg</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/hammer/hammer_34.jpg</t>
         </is>
       </c>
       <c r="H163" t="inlineStr"/>
@@ -13203,12 +13203,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/jacket/jacket_33.jpg</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="H164" t="inlineStr"/>
@@ -13290,12 +13290,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/jacket/jacket_33.jpg</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="H165" t="inlineStr"/>
@@ -13359,12 +13359,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="H166" t="inlineStr"/>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="H167" t="inlineStr"/>
@@ -13515,12 +13515,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/chair/chair_39.jpg</t>
         </is>
       </c>
       <c r="H168" t="inlineStr"/>
@@ -13602,12 +13602,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/chair/chair_39.jpg</t>
         </is>
       </c>
       <c r="H169" t="inlineStr"/>
@@ -13671,12 +13671,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/hammer/hammer_34.jpg</t>
         </is>
       </c>
       <c r="H170" t="inlineStr"/>
@@ -13758,12 +13758,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/hammer/hammer_34.jpg</t>
         </is>
       </c>
       <c r="H171" t="inlineStr"/>
@@ -13827,12 +13827,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/hand/hand_11.jpg</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="H172" t="inlineStr"/>
@@ -13914,12 +13914,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/hand/hand_11.jpg</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="H173" t="inlineStr"/>
@@ -13983,12 +13983,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="H174" t="inlineStr"/>
@@ -14070,12 +14070,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="H175" t="inlineStr"/>
@@ -14139,12 +14139,12 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bicycle/bicycle_36.jpg</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/chair/chair_39.jpg</t>
         </is>
       </c>
       <c r="H176" t="inlineStr"/>
@@ -14226,12 +14226,12 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bicycle/bicycle_36.jpg</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/chair/chair_39.jpg</t>
         </is>
       </c>
       <c r="H177" t="inlineStr"/>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="H178" t="inlineStr"/>
@@ -14382,12 +14382,12 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="H179" t="inlineStr"/>
@@ -14451,12 +14451,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/hand/hand_11.jpg</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/hammer/hammer_34.jpg</t>
         </is>
       </c>
       <c r="H180" t="inlineStr"/>
@@ -14538,12 +14538,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/hand/hand_11.jpg</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/hammer/hammer_34.jpg</t>
         </is>
       </c>
       <c r="H181" t="inlineStr"/>
@@ -14607,12 +14607,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/chair/chair_39.jpg</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="H182" t="inlineStr"/>
@@ -14694,12 +14694,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/chair/chair_39.jpg</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="H183" t="inlineStr"/>
@@ -14763,12 +14763,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/jacket/jacket_33.jpg</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bicycle/bicycle_36.jpg</t>
         </is>
       </c>
       <c r="H184" t="inlineStr"/>
@@ -14850,12 +14850,12 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/jacket/jacket_33.jpg</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bicycle/bicycle_36.jpg</t>
         </is>
       </c>
       <c r="H185" t="inlineStr"/>
@@ -14919,12 +14919,12 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="H186" t="inlineStr"/>
@@ -15006,12 +15006,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="H187" t="inlineStr"/>
@@ -15075,12 +15075,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="H188" t="inlineStr"/>
@@ -15162,12 +15162,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="H189" t="inlineStr"/>
@@ -15231,12 +15231,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/hand/hand_11.jpg</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/chair/chair_39.jpg</t>
         </is>
       </c>
       <c r="H190" t="inlineStr"/>
@@ -15318,12 +15318,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/hand/hand_11.jpg</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/chair/chair_39.jpg</t>
         </is>
       </c>
       <c r="H191" t="inlineStr"/>
@@ -15387,12 +15387,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/hammer/hammer_34.jpg</t>
         </is>
       </c>
       <c r="H192" t="inlineStr"/>
@@ -15474,12 +15474,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/hammer/hammer_34.jpg</t>
         </is>
       </c>
       <c r="H193" t="inlineStr"/>
@@ -15543,12 +15543,12 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="H194" t="inlineStr"/>
@@ -15630,12 +15630,12 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="H195" t="inlineStr"/>
@@ -15699,12 +15699,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bicycle/bicycle_36.jpg</t>
         </is>
       </c>
       <c r="H196" t="inlineStr"/>
@@ -15786,12 +15786,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bicycle/bicycle_36.jpg</t>
         </is>
       </c>
       <c r="H197" t="inlineStr"/>
@@ -15855,12 +15855,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/chair/chair_39.jpg</t>
         </is>
       </c>
       <c r="H198" t="inlineStr"/>
@@ -15942,12 +15942,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/chair/chair_39.jpg</t>
         </is>
       </c>
       <c r="H199" t="inlineStr"/>
@@ -16011,12 +16011,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/jacket/jacket_33.jpg</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/hand/hand_11.jpg</t>
         </is>
       </c>
       <c r="H200" t="inlineStr"/>
@@ -16098,12 +16098,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/jacket/jacket_33.jpg</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/hand/hand_11.jpg</t>
         </is>
       </c>
       <c r="H201" t="inlineStr"/>
@@ -16167,12 +16167,12 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/chair/chair_39.jpg</t>
         </is>
       </c>
       <c r="H202" t="inlineStr"/>
@@ -16254,12 +16254,12 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/chair/chair_39.jpg</t>
         </is>
       </c>
       <c r="H203" t="inlineStr"/>
@@ -16323,12 +16323,12 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/hand/hand_11.jpg</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/jacket/jacket_33.jpg</t>
         </is>
       </c>
       <c r="H204" t="inlineStr"/>
@@ -16410,12 +16410,12 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/hand/hand_11.jpg</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/jacket/jacket_33.jpg</t>
         </is>
       </c>
       <c r="H205" t="inlineStr"/>
@@ -16479,12 +16479,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="H206" t="inlineStr"/>
@@ -16566,12 +16566,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="H207" t="inlineStr"/>
@@ -16635,12 +16635,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/hammer/hammer_34.jpg</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="H208" t="inlineStr"/>
@@ -16722,12 +16722,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/hammer/hammer_34.jpg</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="H209" t="inlineStr"/>
@@ -16791,12 +16791,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bicycle/bicycle_36.jpg</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="H210" t="inlineStr"/>
@@ -16878,12 +16878,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bicycle/bicycle_36.jpg</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="H211" t="inlineStr"/>
@@ -16947,12 +16947,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="H212" t="inlineStr"/>
@@ -17034,12 +17034,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="H213" t="inlineStr"/>
@@ -17103,12 +17103,12 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/hand/hand_11.jpg</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/chair/chair_39.jpg</t>
         </is>
       </c>
       <c r="H214" t="inlineStr"/>
@@ -17190,12 +17190,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/hand/hand_11.jpg</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/chair/chair_39.jpg</t>
         </is>
       </c>
       <c r="H215" t="inlineStr"/>
@@ -17259,12 +17259,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/hammer/hammer_34.jpg</t>
         </is>
       </c>
       <c r="H216" t="inlineStr"/>
@@ -17346,12 +17346,12 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/hammer/hammer_34.jpg</t>
         </is>
       </c>
       <c r="H217" t="inlineStr"/>
@@ -17415,12 +17415,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/jacket/jacket_33.jpg</t>
         </is>
       </c>
       <c r="H218" t="inlineStr"/>
@@ -17502,12 +17502,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/jacket/jacket_33.jpg</t>
         </is>
       </c>
       <c r="H219" t="inlineStr"/>
@@ -17571,12 +17571,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="H220" t="inlineStr"/>
@@ -17658,12 +17658,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="H221" t="inlineStr"/>
@@ -17727,12 +17727,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/hammer/hammer_34.jpg</t>
         </is>
       </c>
       <c r="H222" t="inlineStr"/>
@@ -17814,12 +17814,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/hammer/hammer_34.jpg</t>
         </is>
       </c>
       <c r="H223" t="inlineStr"/>
@@ -17883,12 +17883,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bicycle/bicycle_36.jpg</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/chair/chair_39.jpg</t>
         </is>
       </c>
       <c r="H224" t="inlineStr"/>
@@ -17970,12 +17970,12 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bicycle/bicycle_36.jpg</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/chair/chair_39.jpg</t>
         </is>
       </c>
       <c r="H225" t="inlineStr"/>
@@ -18039,12 +18039,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="H226" t="inlineStr"/>
@@ -18126,12 +18126,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="H227" t="inlineStr"/>
@@ -18195,12 +18195,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bicycle/bicycle_36.jpg</t>
         </is>
       </c>
       <c r="H228" t="inlineStr"/>
@@ -18282,12 +18282,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_27.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bicycle/bicycle_36.jpg</t>
         </is>
       </c>
       <c r="H229" t="inlineStr"/>
@@ -18351,12 +18351,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="H230" t="inlineStr"/>
@@ -18438,12 +18438,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="H231" t="inlineStr"/>
@@ -18507,12 +18507,12 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/hand/hand_11.jpg</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/hammer/hammer_34.jpg</t>
         </is>
       </c>
       <c r="H232" t="inlineStr"/>
@@ -18594,12 +18594,12 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/hand/hand_11.jpg</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/hammer/hammer_34.jpg</t>
         </is>
       </c>
       <c r="H233" t="inlineStr"/>
@@ -18663,12 +18663,12 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/chair/chair_39.jpg</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="H234" t="inlineStr"/>
@@ -18750,12 +18750,12 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_14.jpg</t>
+          <t>stimuli/chair/chair_39.jpg</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_06.jpg</t>
+          <t>stimuli/bread/bread_01.jpg</t>
         </is>
       </c>
       <c r="H235" t="inlineStr"/>
@@ -18819,12 +18819,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/jacket/jacket_33.jpg</t>
         </is>
       </c>
       <c r="H236" t="inlineStr"/>
@@ -18906,12 +18906,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_10.jpg</t>
+          <t>stimuli/ball/ball_28.jpg</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_27.jpg</t>
+          <t>stimuli/jacket/jacket_33.jpg</t>
         </is>
       </c>
       <c r="H237" t="inlineStr"/>
@@ -18975,12 +18975,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bicycle/bicycle_36.jpg</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="H238" t="inlineStr"/>
@@ -19062,12 +19062,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_12.jpg</t>
+          <t>stimuli/bicycle/bicycle_36.jpg</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_08.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="H239" t="inlineStr"/>
@@ -19131,12 +19131,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/hand/hand_11.jpg</t>
         </is>
       </c>
       <c r="H240" t="inlineStr"/>
@@ -19218,12 +19218,12 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>stimuli/house/house_35.jpg</t>
+          <t>stimuli/house/house_22.jpg</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/hand/hand_11.jpg</t>
         </is>
       </c>
       <c r="H241" t="inlineStr"/>
